--- a/documents/originals/www.ipa.go.jp/security/scs/rcu1hd0000007a2i-att/SCS-410AP-self-assess-sheet-v1.0.xlsx
+++ b/documents/originals/www.ipa.go.jp/security/scs/rcu1hd0000007a2i-att/SCS-410AP-self-assess-sheet-v1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9111229-80F2-4578-B0D5-2717EC9222C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196661AB-B0CF-4ECD-8EFF-9AD5F3367BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="180" windowWidth="28575" windowHeight="15270" tabRatio="738" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11835" tabRatio="738" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="【★3・★4共通】適用範囲に関する質問事項" sheetId="30" r:id="rId1"/>
@@ -5694,10 +5694,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>③やむを得ずサポート切れのものを利用する場合は更改計画を策定し、更改までの間、No.4-4-4-2で求める脆弱性悪用リスクの低減策を実施していること。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>OS及びソフトウェアのライセンス・サポートが有効でない場合に実施している脆弱性悪用リスクの低減策の内容を回答してください。</t>
     <rPh sb="30" eb="32">
       <t>ジッシ</t>
@@ -6171,22 +6167,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>情報機器、OS及びソフトウェアについて、以下の状態とすること。
-‒ ライセンスが付与され、サポートされている。
-‒ サポートが終了した場合に削除されるか、又はインターネットとの全てのトラフィックを遮断することで適用範囲から削除される。
-‒ やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを軽減する対策を実施している。
-‒ 可能であれば、自動アップデートが有効化されている。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>・情報機器、OS及びソフトウェアについて、以下の状態とすること。
-‒ ライセンスが付与され、サポートされている。
-‒ サポートが終了した場合に削除されるか、又はインターネットとの全てのトラフィックを遮断することで適用範囲から削除される。
-‒ やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを軽減する対策を実施している。
-‒ 可能であれば、自動アップデートが有効化されている。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>適合基準
 ※「★3・★4自己評価等ガイド」別紙及び「★4第三者評価ガイド」別紙で示される適合基準と同一</t>
     <rPh sb="0" eb="4">
@@ -7079,10 +7059,6 @@
   </si>
   <si>
     <t xml:space="preserve">②IT資産管理台帳、構成管理情報等を確認し、全てのOS及びソフトウェアについてサポートのあるものを利用していることを確認する。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③やむを得ずサポート切れのものを利用している場合は更改計画を策定し、更改までの間、No.4-4-4-2で求める脆弱性悪用リスクの低減策を実施していることを確認する。
 </t>
   </si>
   <si>
@@ -7730,6 +7706,35 @@
     <t>情報機器及びソフトウェアの挙動監視</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>・情報機器、OS及びソフトウェアについて、以下の状態とすること。
+‒ ライセンスが付与され、サポートされている。
+‒ サポートが終了した場合に削除されるか、又はインターネットとの全てのトラフィックを遮断することで適用範囲から削除される。
+‒ やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを低減する対策を実施している。
+‒ 可能であれば、自動アップデートが有効化されている。</t>
+  </si>
+  <si>
+    <t>情報機器、OS及びソフトウェアについて、以下の状態とすること。
+‒ ライセンスが付与され、サポートされている。
+‒ サポートが終了した場合に削除されるか、又はインターネットとの全てのトラフィックを遮断することで適用範囲から削除される。
+‒ やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを低減する対策を実施している。
+‒ 可能であれば、自動アップデートが有効化されている。</t>
+  </si>
+  <si>
+    <t>③やむを得ずサポート切れのものを利用する場合は更改計画を策定し、更改までの間、No.4-4-4-2の適合基準で求める脆弱性悪用リスクの低減策を実施していること。</t>
+    <rPh sb="50" eb="54">
+      <t>テキゴウキジュン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">③やむを得ずサポート切れのものを利用している場合は更改計画を策定し、更改までの間、No.4-4-4-2の適合基準で求める脆弱性悪用リスクの低減策を実施していることを確認する。
+</t>
+    <rPh sb="52" eb="56">
+      <t>テキゴウキジュン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -7738,7 +7743,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;月&quot;dd&quot;日&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9056,7 +9061,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="6.75" style="8" customWidth="1"/>
     <col min="2" max="2" width="52.25" style="8" customWidth="1"/>
@@ -9065,13 +9070,13 @@
     <col min="5" max="16384" width="8.625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="24">
       <c r="A1" s="7" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.TEXTAFTER(CELL("filename",A1),"]")</f>
         <v>【★3・★4共通】適用範囲に関する質問事項</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -9085,7 +9090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="175.5">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -9093,23 +9098,23 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D3" s="9"/>
     </row>
-    <row r="4" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="136.5">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="D4" s="10"/>
     </row>
-    <row r="5" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="136.5">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9117,11 +9122,11 @@
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="136.5">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -9129,11 +9134,11 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="214.5">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -9141,11 +9146,11 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="136.5">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -9153,11 +9158,11 @@
         <v>14</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" spans="1:4" ht="156" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="156">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -9165,11 +9170,11 @@
         <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="136.5">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -9177,11 +9182,11 @@
         <v>18</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" spans="1:4" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="97.5">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -9189,11 +9194,11 @@
         <v>20</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D11" s="10"/>
     </row>
-    <row r="12" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="136.5">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -9201,11 +9206,11 @@
         <v>27</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" spans="1:4" ht="156" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="156">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -9213,11 +9218,11 @@
         <v>28</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D13" s="10"/>
     </row>
-    <row r="14" spans="1:4" ht="156" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="156">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
@@ -9225,48 +9230,48 @@
         <v>29</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" spans="1:4" ht="117" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="117">
       <c r="A15" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D15" s="10"/>
     </row>
-    <row r="16" spans="1:4" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="97.5">
       <c r="A16" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="D16" s="10"/>
     </row>
-    <row r="17" spans="1:4" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="136.5">
       <c r="A17" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="D17" s="10"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" formatColumns="0" formatRows="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3" xr:uid="{DC9A6DD1-A619-465D-A65D-7949B3CB0BC0}">
@@ -9293,7 +9298,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U134"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="12" customWidth="1" outlineLevel="1"/>
     <col min="2" max="2" width="12.25" style="12" customWidth="1" outlineLevel="1"/>
@@ -9318,7 +9323,7 @@
     <col min="22" max="16384" width="8.625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18">
       <c r="A1" s="11"/>
       <c r="K1" s="13"/>
       <c r="M1" s="12"/>
@@ -9329,7 +9334,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="33"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18">
       <c r="K2" s="13"/>
       <c r="M2" s="12"/>
       <c r="O2" s="37" t="s">
@@ -9339,7 +9344,7 @@
       <c r="Q2" s="63"/>
       <c r="R2" s="64"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18">
       <c r="K3" s="13"/>
       <c r="M3" s="12"/>
       <c r="O3" s="38" t="s">
@@ -9349,7 +9354,7 @@
       <c r="Q3" s="66"/>
       <c r="R3" s="67"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18">
       <c r="K4" s="13"/>
       <c r="M4" s="12"/>
       <c r="O4" s="38" t="s">
@@ -9359,7 +9364,7 @@
       <c r="Q4" s="66"/>
       <c r="R4" s="67"/>
     </row>
-    <row r="5" spans="1:18" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="20.25" thickBot="1">
       <c r="K5" s="13"/>
       <c r="M5" s="12"/>
       <c r="O5" s="35" t="s">
@@ -9369,37 +9374,37 @@
       <c r="Q5" s="69"/>
       <c r="R5" s="70"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18">
       <c r="K6" s="13"/>
       <c r="M6" s="12"/>
       <c r="O6" s="31" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="32"/>
       <c r="R6" s="33"/>
     </row>
-    <row r="7" spans="1:18" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" ht="58.5">
       <c r="K7" s="13"/>
       <c r="M7" s="12"/>
       <c r="O7" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="P7" s="65"/>
       <c r="Q7" s="66"/>
       <c r="R7" s="67"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18">
       <c r="K8" s="13"/>
       <c r="M8" s="12"/>
       <c r="O8" s="36" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="P8" s="65"/>
       <c r="Q8" s="66"/>
       <c r="R8" s="67"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18">
       <c r="K9" s="13"/>
       <c r="M9" s="12"/>
       <c r="O9" s="36" t="s">
@@ -9409,7 +9414,7 @@
       <c r="Q9" s="66"/>
       <c r="R9" s="67"/>
     </row>
-    <row r="10" spans="1:18" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="20.25" thickBot="1">
       <c r="K10" s="13"/>
       <c r="M10" s="12"/>
       <c r="O10" s="39" t="s">
@@ -9419,57 +9424,57 @@
       <c r="Q10" s="72"/>
       <c r="R10" s="73"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18">
       <c r="K11" s="13"/>
       <c r="M11" s="12"/>
       <c r="O11" s="31" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="P11" s="32"/>
       <c r="Q11" s="32"/>
       <c r="R11" s="33"/>
     </row>
-    <row r="12" spans="1:18" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" ht="58.5">
       <c r="K12" s="13"/>
       <c r="M12" s="12"/>
       <c r="O12" s="34" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="P12" s="65"/>
       <c r="Q12" s="66"/>
       <c r="R12" s="67"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18">
       <c r="K13" s="13"/>
       <c r="M13" s="12"/>
       <c r="O13" s="36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="P13" s="65"/>
       <c r="Q13" s="66"/>
       <c r="R13" s="67"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18">
       <c r="K14" s="13"/>
       <c r="M14" s="12"/>
       <c r="O14" s="36" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P14" s="65"/>
       <c r="Q14" s="66"/>
       <c r="R14" s="67"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18">
       <c r="K15" s="13"/>
       <c r="M15" s="12"/>
       <c r="O15" s="36" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="P15" s="65"/>
       <c r="Q15" s="66"/>
       <c r="R15" s="67"/>
     </row>
-    <row r="16" spans="1:18" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18" ht="20.25" thickBot="1">
       <c r="K16" s="13"/>
       <c r="M16" s="12"/>
       <c r="O16" s="39" t="s">
@@ -9479,7 +9484,7 @@
       <c r="Q16" s="72"/>
       <c r="R16" s="73"/>
     </row>
-    <row r="17" spans="1:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" ht="24">
       <c r="A17" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.TEXTAFTER(CELL("filename",A1),"]")</f>
         <v>【★3用】アセスメントシート</v>
@@ -9489,7 +9494,7 @@
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
     </row>
-    <row r="18" spans="1:21" s="24" customFormat="1" ht="78" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" s="24" customFormat="1" ht="78">
       <c r="A18" s="18" t="s">
         <v>38</v>
       </c>
@@ -9524,16 +9529,16 @@
         <v>50</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="N18" s="21" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="P18" s="22" t="s">
         <v>51</v>
@@ -9545,7 +9550,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" ht="136.5">
       <c r="A19" s="25">
         <v>1</v>
       </c>
@@ -9562,7 +9567,7 @@
         <v>57</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>59</v>
@@ -9585,7 +9590,7 @@
         <v>64</v>
       </c>
       <c r="O19" s="26" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="P19" s="14"/>
       <c r="Q19" s="16" t="s">
@@ -9594,7 +9599,7 @@
       <c r="R19" s="14"/>
       <c r="U19" s="13"/>
     </row>
-    <row r="20" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" ht="156">
       <c r="A20" s="80">
         <f t="shared" ref="A20:G22" si="0">A19</f>
         <v>1</v>
@@ -9645,14 +9650,14 @@
         <v>66</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="P20" s="14"/>
       <c r="Q20" s="28"/>
       <c r="R20" s="15"/>
       <c r="U20" s="13"/>
     </row>
-    <row r="21" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" ht="136.5">
       <c r="A21" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9701,7 +9706,7 @@
         <v>69</v>
       </c>
       <c r="O21" s="26" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="P21" s="14"/>
       <c r="Q21" s="16" t="s">
@@ -9710,7 +9715,7 @@
       <c r="R21" s="14"/>
       <c r="U21" s="13"/>
     </row>
-    <row r="22" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" ht="117">
       <c r="A22" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9759,7 +9764,7 @@
         <v>73</v>
       </c>
       <c r="O22" s="26" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="P22" s="14"/>
       <c r="Q22" s="27" t="s">
@@ -9768,7 +9773,7 @@
       <c r="R22" s="14"/>
       <c r="U22" s="13"/>
     </row>
-    <row r="23" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" ht="136.5">
       <c r="A23" s="80">
         <f t="shared" ref="A23:D23" si="3">A22</f>
         <v>1</v>
@@ -9813,7 +9818,7 @@
         <v>80</v>
       </c>
       <c r="O23" s="26" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="P23" s="14"/>
       <c r="Q23" s="16" t="s">
@@ -9822,7 +9827,7 @@
       <c r="R23" s="14"/>
       <c r="U23" s="13"/>
     </row>
-    <row r="24" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" ht="117">
       <c r="A24" s="80">
         <f t="shared" ref="A24:G24" si="4">A23</f>
         <v>1</v>
@@ -9871,7 +9876,7 @@
         <v>84</v>
       </c>
       <c r="O24" s="26" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="P24" s="14"/>
       <c r="Q24" s="16" t="s">
@@ -9880,7 +9885,7 @@
       <c r="R24" s="14"/>
       <c r="U24" s="13"/>
     </row>
-    <row r="25" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" ht="117">
       <c r="A25" s="80">
         <f t="shared" ref="A25:B25" si="5">A24</f>
         <v>1</v>
@@ -9923,7 +9928,7 @@
         <v>93</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="P25" s="14"/>
       <c r="Q25" s="16" t="s">
@@ -9932,7 +9937,7 @@
       <c r="R25" s="14"/>
       <c r="U25" s="13"/>
     </row>
-    <row r="26" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" ht="136.5">
       <c r="A26" s="80">
         <f t="shared" ref="A26:G27" si="6">A25</f>
         <v>1</v>
@@ -9966,7 +9971,7 @@
         <v>★3</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="J26" s="26" t="s">
         <v>96</v>
@@ -9981,7 +9986,7 @@
         <v>97</v>
       </c>
       <c r="O26" s="26" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="P26" s="14"/>
       <c r="Q26" s="16" t="s">
@@ -9990,7 +9995,7 @@
       <c r="R26" s="14"/>
       <c r="U26" s="13"/>
     </row>
-    <row r="27" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" ht="156">
       <c r="A27" s="80">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -10039,7 +10044,7 @@
         <v>101</v>
       </c>
       <c r="O27" s="26" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="P27" s="14"/>
       <c r="Q27" s="16" t="s">
@@ -10048,7 +10053,7 @@
       <c r="R27" s="14"/>
       <c r="U27" s="13"/>
     </row>
-    <row r="28" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" ht="117">
       <c r="A28" s="25">
         <v>2</v>
       </c>
@@ -10089,7 +10094,7 @@
         <v>111</v>
       </c>
       <c r="O28" s="26" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="P28" s="14"/>
       <c r="Q28" s="16" t="s">
@@ -10098,7 +10103,7 @@
       <c r="R28" s="14"/>
       <c r="U28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" ht="97.5">
       <c r="A29" s="80">
         <f t="shared" ref="A29:G30" si="8">A28</f>
         <v>2</v>
@@ -10149,14 +10154,14 @@
         <v>113</v>
       </c>
       <c r="O29" s="26" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="P29" s="14"/>
       <c r="Q29" s="28"/>
       <c r="R29" s="15"/>
       <c r="U29" s="13"/>
     </row>
-    <row r="30" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" ht="117">
       <c r="A30" s="80">
         <f t="shared" si="8"/>
         <v>2</v>
@@ -10205,7 +10210,7 @@
         <v>116</v>
       </c>
       <c r="O30" s="26" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="P30" s="14"/>
       <c r="Q30" s="27" t="s">
@@ -10214,7 +10219,7 @@
       <c r="R30" s="14"/>
       <c r="U30" s="13"/>
     </row>
-    <row r="31" spans="1:21" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" ht="214.5">
       <c r="A31" s="80">
         <f t="shared" ref="A31:D32" si="10">A30</f>
         <v>2</v>
@@ -10259,7 +10264,7 @@
         <v>123</v>
       </c>
       <c r="O31" s="26" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="P31" s="14"/>
       <c r="Q31" s="16" t="s">
@@ -10268,7 +10273,7 @@
       <c r="R31" s="14"/>
       <c r="U31" s="13"/>
     </row>
-    <row r="32" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" ht="156">
       <c r="A32" s="80">
         <f t="shared" si="10"/>
         <v>2</v>
@@ -10313,7 +10318,7 @@
         <v>130</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="P32" s="14"/>
       <c r="Q32" s="16" t="s">
@@ -10322,7 +10327,7 @@
       <c r="R32" s="14"/>
       <c r="U32" s="13"/>
     </row>
-    <row r="33" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:21" ht="117">
       <c r="A33" s="41">
         <v>3</v>
       </c>
@@ -10362,7 +10367,7 @@
         <v>141</v>
       </c>
       <c r="O33" s="26" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P33" s="14"/>
       <c r="Q33" s="16" t="s">
@@ -10371,7 +10376,7 @@
       <c r="R33" s="14"/>
       <c r="U33" s="13"/>
     </row>
-    <row r="34" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:21" ht="97.5">
       <c r="A34" s="79">
         <f t="shared" ref="A34:G39" si="11">A33</f>
         <v>3</v>
@@ -10422,14 +10427,14 @@
         <v>143</v>
       </c>
       <c r="O34" s="26" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="P34" s="14"/>
       <c r="Q34" s="28"/>
       <c r="R34" s="15"/>
       <c r="U34" s="13"/>
     </row>
-    <row r="35" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:21" ht="117">
       <c r="A35" s="79">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -10478,7 +10483,7 @@
         <v>146</v>
       </c>
       <c r="O35" s="26" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="P35" s="14"/>
       <c r="Q35" s="16" t="s">
@@ -10487,7 +10492,7 @@
       <c r="R35" s="14"/>
       <c r="U35" s="13"/>
     </row>
-    <row r="36" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:21" ht="97.5">
       <c r="A36" s="79">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -10538,14 +10543,14 @@
         <v>148</v>
       </c>
       <c r="O36" s="26" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="P36" s="14"/>
       <c r="Q36" s="28"/>
       <c r="R36" s="15"/>
       <c r="U36" s="13"/>
     </row>
-    <row r="37" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:21" ht="97.5">
       <c r="A37" s="79">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -10594,7 +10599,7 @@
         <v>151</v>
       </c>
       <c r="O37" s="26" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="P37" s="14"/>
       <c r="Q37" s="16" t="s">
@@ -10603,7 +10608,7 @@
       <c r="R37" s="14"/>
       <c r="U37" s="13"/>
     </row>
-    <row r="38" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:21" ht="117">
       <c r="A38" s="79">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -10654,14 +10659,14 @@
         <v>153</v>
       </c>
       <c r="O38" s="26" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="P38" s="14"/>
       <c r="Q38" s="28"/>
       <c r="R38" s="15"/>
       <c r="U38" s="13"/>
     </row>
-    <row r="39" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" ht="136.5">
       <c r="A39" s="79">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -10710,7 +10715,7 @@
         <v>156</v>
       </c>
       <c r="O39" s="26" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="P39" s="14"/>
       <c r="Q39" s="27" t="s">
@@ -10719,7 +10724,7 @@
       <c r="R39" s="14"/>
       <c r="U39" s="13"/>
     </row>
-    <row r="40" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" ht="117">
       <c r="A40" s="79">
         <f t="shared" ref="A40:D40" si="14">A39</f>
         <v>3</v>
@@ -10764,7 +10769,7 @@
         <v>163</v>
       </c>
       <c r="O40" s="26" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="P40" s="14"/>
       <c r="Q40" s="16" t="s">
@@ -10773,7 +10778,7 @@
       <c r="R40" s="14"/>
       <c r="U40" s="13"/>
     </row>
-    <row r="41" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" ht="117">
       <c r="A41" s="79">
         <f t="shared" ref="A41:G43" si="15">A40</f>
         <v>3</v>
@@ -10824,14 +10829,14 @@
         <v>165</v>
       </c>
       <c r="O41" s="26" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="P41" s="14"/>
       <c r="Q41" s="28"/>
       <c r="R41" s="15"/>
       <c r="U41" s="13"/>
     </row>
-    <row r="42" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:21" ht="117">
       <c r="A42" s="79">
         <f t="shared" si="15"/>
         <v>3</v>
@@ -10880,7 +10885,7 @@
         <v>168</v>
       </c>
       <c r="O42" s="26" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="16" t="s">
@@ -10889,7 +10894,7 @@
       <c r="R42" s="14"/>
       <c r="U42" s="13"/>
     </row>
-    <row r="43" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:21" ht="117">
       <c r="A43" s="79">
         <f t="shared" si="15"/>
         <v>3</v>
@@ -10940,14 +10945,14 @@
         <v>170</v>
       </c>
       <c r="O43" s="26" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="P43" s="14"/>
       <c r="Q43" s="28"/>
       <c r="R43" s="15"/>
       <c r="U43" s="13"/>
     </row>
-    <row r="44" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" ht="97.5">
       <c r="A44" s="79">
         <f t="shared" ref="A44:D44" si="18">A43</f>
         <v>3</v>
@@ -10992,7 +10997,7 @@
         <v>176</v>
       </c>
       <c r="O44" s="26" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="P44" s="14"/>
       <c r="Q44" s="16" t="s">
@@ -11001,7 +11006,7 @@
       <c r="R44" s="14"/>
       <c r="U44" s="13"/>
     </row>
-    <row r="45" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" ht="136.5">
       <c r="A45" s="79">
         <f t="shared" ref="A45:G46" si="19">A44</f>
         <v>3</v>
@@ -11052,14 +11057,14 @@
         <v>178</v>
       </c>
       <c r="O45" s="26" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="P45" s="14"/>
       <c r="Q45" s="28"/>
       <c r="R45" s="15"/>
       <c r="U45" s="13"/>
     </row>
-    <row r="46" spans="1:21" ht="195" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:21" ht="195">
       <c r="A46" s="79">
         <f t="shared" si="19"/>
         <v>3</v>
@@ -11105,10 +11110,10 @@
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
       <c r="N46" s="26" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="O46" s="26" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="P46" s="14"/>
       <c r="Q46" s="16" t="s">
@@ -11117,7 +11122,7 @@
       <c r="R46" s="14"/>
       <c r="U46" s="13"/>
     </row>
-    <row r="47" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:21" ht="117">
       <c r="A47" s="79">
         <f t="shared" ref="A47:D47" si="21">A46</f>
         <v>3</v>
@@ -11162,7 +11167,7 @@
         <v>187</v>
       </c>
       <c r="O47" s="26" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="P47" s="14"/>
       <c r="Q47" s="16" t="s">
@@ -11171,7 +11176,7 @@
       <c r="R47" s="14"/>
       <c r="U47" s="13"/>
     </row>
-    <row r="48" spans="1:21" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:21" ht="175.5">
       <c r="A48" s="79">
         <f t="shared" ref="A48:G50" si="22">A47</f>
         <v>3</v>
@@ -11226,14 +11231,14 @@
         <v>189</v>
       </c>
       <c r="O48" s="26" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="P48" s="14"/>
       <c r="Q48" s="28"/>
       <c r="R48" s="15"/>
       <c r="U48" s="13"/>
     </row>
-    <row r="49" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" ht="117">
       <c r="A49" s="79">
         <f t="shared" si="22"/>
         <v>3</v>
@@ -11282,7 +11287,7 @@
         <v>192</v>
       </c>
       <c r="O49" s="26" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="P49" s="14"/>
       <c r="Q49" s="27" t="s">
@@ -11291,7 +11296,7 @@
       <c r="R49" s="14"/>
       <c r="U49" s="13"/>
     </row>
-    <row r="50" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:21" ht="136.5">
       <c r="A50" s="79">
         <f t="shared" si="22"/>
         <v>3</v>
@@ -11340,7 +11345,7 @@
         <v>196</v>
       </c>
       <c r="O50" s="26" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="P50" s="14"/>
       <c r="Q50" s="16" t="s">
@@ -11349,7 +11354,7 @@
       <c r="R50" s="14"/>
       <c r="U50" s="13"/>
     </row>
-    <row r="51" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:21" ht="136.5">
       <c r="A51" s="42">
         <v>4</v>
       </c>
@@ -11389,16 +11394,16 @@
         <v>207</v>
       </c>
       <c r="O51" s="26" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="P51" s="14"/>
       <c r="Q51" s="16" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="R51" s="14"/>
       <c r="U51" s="13"/>
     </row>
-    <row r="52" spans="1:21" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:21" ht="214.5">
       <c r="A52" s="77">
         <f t="shared" ref="A52:G54" si="24">A51</f>
         <v>4</v>
@@ -11447,7 +11452,7 @@
         <v>210</v>
       </c>
       <c r="O52" s="26" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="P52" s="14"/>
       <c r="Q52" s="16" t="s">
@@ -11456,7 +11461,7 @@
       <c r="R52" s="14"/>
       <c r="U52" s="13"/>
     </row>
-    <row r="53" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:21" ht="117">
       <c r="A53" s="77">
         <f t="shared" si="24"/>
         <v>4</v>
@@ -11505,7 +11510,7 @@
         <v>214</v>
       </c>
       <c r="O53" s="26" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="16" t="s">
@@ -11514,7 +11519,7 @@
       <c r="R53" s="14"/>
       <c r="U53" s="13"/>
     </row>
-    <row r="54" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:21" ht="136.5">
       <c r="A54" s="77">
         <f t="shared" si="24"/>
         <v>4</v>
@@ -11563,16 +11568,16 @@
         <v>218</v>
       </c>
       <c r="O54" s="26" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="P54" s="14"/>
       <c r="Q54" s="16" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="R54" s="14"/>
       <c r="U54" s="13"/>
     </row>
-    <row r="55" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:21" ht="117">
       <c r="A55" s="77">
         <f t="shared" ref="A55:D55" si="27">A54</f>
         <v>4</v>
@@ -11617,16 +11622,16 @@
         <v>224</v>
       </c>
       <c r="O55" s="26" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="P55" s="14"/>
       <c r="Q55" s="16" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="R55" s="14"/>
       <c r="U55" s="13"/>
     </row>
-    <row r="56" spans="1:21" ht="234" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:21" ht="234">
       <c r="A56" s="77">
         <f t="shared" ref="A56:G63" si="28">A55</f>
         <v>4</v>
@@ -11675,7 +11680,7 @@
         <v>227</v>
       </c>
       <c r="O56" s="26" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="P56" s="14"/>
       <c r="Q56" s="16" t="s">
@@ -11684,7 +11689,7 @@
       <c r="R56" s="14"/>
       <c r="U56" s="13"/>
     </row>
-    <row r="57" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:21" ht="117">
       <c r="A57" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -11733,7 +11738,7 @@
         <v>231</v>
       </c>
       <c r="O57" s="26" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="P57" s="14"/>
       <c r="Q57" s="16" t="s">
@@ -11742,7 +11747,7 @@
       <c r="R57" s="14"/>
       <c r="U57" s="13"/>
     </row>
-    <row r="58" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:21" ht="136.5">
       <c r="A58" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -11791,7 +11796,7 @@
         <v>235</v>
       </c>
       <c r="O58" s="26" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="P58" s="14"/>
       <c r="Q58" s="16" t="s">
@@ -11800,7 +11805,7 @@
       <c r="R58" s="14"/>
       <c r="U58" s="13"/>
     </row>
-    <row r="59" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:21" ht="136.5">
       <c r="A59" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -11849,7 +11854,7 @@
         <v>239</v>
       </c>
       <c r="O59" s="26" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="P59" s="14"/>
       <c r="Q59" s="16" t="s">
@@ -11858,7 +11863,7 @@
       <c r="R59" s="14"/>
       <c r="U59" s="13"/>
     </row>
-    <row r="60" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:21" ht="117">
       <c r="A60" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -11907,7 +11912,7 @@
         <v>243</v>
       </c>
       <c r="O60" s="26" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="P60" s="14"/>
       <c r="Q60" s="16" t="s">
@@ -11916,7 +11921,7 @@
       <c r="R60" s="14"/>
       <c r="U60" s="13"/>
     </row>
-    <row r="61" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:21" ht="117">
       <c r="A61" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -11965,7 +11970,7 @@
         <v>247</v>
       </c>
       <c r="O61" s="26" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="P61" s="14"/>
       <c r="Q61" s="16" t="s">
@@ -11974,7 +11979,7 @@
       <c r="R61" s="14"/>
       <c r="U61" s="13"/>
     </row>
-    <row r="62" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:21" ht="117">
       <c r="A62" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -12023,7 +12028,7 @@
         <v>251</v>
       </c>
       <c r="O62" s="26" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="P62" s="14"/>
       <c r="Q62" s="16" t="s">
@@ -12032,7 +12037,7 @@
       <c r="R62" s="14"/>
       <c r="U62" s="13"/>
     </row>
-    <row r="63" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:21" ht="117">
       <c r="A63" s="77">
         <f t="shared" si="28"/>
         <v>4</v>
@@ -12083,7 +12088,7 @@
         <v>253</v>
       </c>
       <c r="O63" s="26" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="P63" s="14"/>
       <c r="Q63" s="16" t="s">
@@ -12092,7 +12097,7 @@
       <c r="R63" s="14"/>
       <c r="U63" s="13"/>
     </row>
-    <row r="64" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:21" ht="136.5">
       <c r="A64" s="77">
         <f t="shared" ref="A64:D64" si="31">A63</f>
         <v>4</v>
@@ -12137,7 +12142,7 @@
         <v>260</v>
       </c>
       <c r="O64" s="26" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="P64" s="14"/>
       <c r="Q64" s="16" t="s">
@@ -12146,7 +12151,7 @@
       <c r="R64" s="14"/>
       <c r="U64" s="13"/>
     </row>
-    <row r="65" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:21" ht="97.5">
       <c r="A65" s="77">
         <f t="shared" ref="A65:G68" si="32">A64</f>
         <v>4</v>
@@ -12195,7 +12200,7 @@
         <v>264</v>
       </c>
       <c r="O65" s="26" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="P65" s="14"/>
       <c r="Q65" s="16" t="s">
@@ -12204,7 +12209,7 @@
       <c r="R65" s="14"/>
       <c r="U65" s="13"/>
     </row>
-    <row r="66" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:21" ht="136.5">
       <c r="A66" s="77">
         <f t="shared" si="32"/>
         <v>4</v>
@@ -12256,7 +12261,7 @@
         <v>①重要な機密情報を取り扱うクラウドサービスにユーザ又は管理者がアクセスする場合、常にNo.4-1-3-3で示す2種類以上の認証要素を利用した多要素認証を使用していること。</v>
       </c>
       <c r="O66" s="26" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="P66" s="14"/>
       <c r="Q66" s="16" t="s">
@@ -12265,7 +12270,7 @@
       <c r="R66" s="14"/>
       <c r="U66" s="13"/>
     </row>
-    <row r="67" spans="1:21" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:21" ht="292.5">
       <c r="A67" s="77">
         <f t="shared" si="32"/>
         <v>4</v>
@@ -12314,14 +12319,14 @@
         <v>269</v>
       </c>
       <c r="O67" s="26" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="P67" s="14"/>
       <c r="Q67" s="28"/>
       <c r="R67" s="15"/>
       <c r="U67" s="13"/>
     </row>
-    <row r="68" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:21" ht="97.5">
       <c r="A68" s="77">
         <f t="shared" si="32"/>
         <v>4</v>
@@ -12370,7 +12375,7 @@
         <v>272</v>
       </c>
       <c r="O68" s="26" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="16" t="s">
@@ -12379,7 +12384,7 @@
       <c r="R68" s="14"/>
       <c r="U68" s="13"/>
     </row>
-    <row r="69" spans="1:21" ht="253.5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:21" ht="253.5">
       <c r="A69" s="77">
         <f t="shared" ref="A69:D69" si="34">A68</f>
         <v>4</v>
@@ -12424,7 +12429,7 @@
         <v>279</v>
       </c>
       <c r="O69" s="26" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="P69" s="14"/>
       <c r="Q69" s="16" t="s">
@@ -12433,7 +12438,7 @@
       <c r="R69" s="14"/>
       <c r="U69" s="13"/>
     </row>
-    <row r="70" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:21" ht="136.5">
       <c r="A70" s="77">
         <f t="shared" ref="A70:G70" si="35">A69</f>
         <v>4</v>
@@ -12482,7 +12487,7 @@
         <v>283</v>
       </c>
       <c r="O70" s="26" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="16" t="s">
@@ -12491,7 +12496,7 @@
       <c r="R70" s="14"/>
       <c r="U70" s="13"/>
     </row>
-    <row r="71" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:21" ht="136.5">
       <c r="A71" s="77">
         <f t="shared" ref="A71:D71" si="36">A70</f>
         <v>4</v>
@@ -12536,7 +12541,7 @@
         <v>290</v>
       </c>
       <c r="O71" s="26" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="P71" s="14"/>
       <c r="Q71" s="16" t="s">
@@ -12545,7 +12550,7 @@
       <c r="R71" s="14"/>
       <c r="U71" s="13"/>
     </row>
-    <row r="72" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:21" ht="136.5">
       <c r="A72" s="77">
         <f t="shared" ref="A72:G76" si="37">A71</f>
         <v>4</v>
@@ -12594,7 +12599,7 @@
         <v>294</v>
       </c>
       <c r="O72" s="26" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="P72" s="14"/>
       <c r="Q72" s="16" t="s">
@@ -12603,7 +12608,7 @@
       <c r="R72" s="14"/>
       <c r="U72" s="13"/>
     </row>
-    <row r="73" spans="1:21" ht="273" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:21" ht="273">
       <c r="A73" s="77">
         <f t="shared" si="37"/>
         <v>4</v>
@@ -12652,7 +12657,7 @@
         <v>298</v>
       </c>
       <c r="O73" s="26" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="P73" s="14"/>
       <c r="Q73" s="16" t="s">
@@ -12661,7 +12666,7 @@
       <c r="R73" s="14"/>
       <c r="U73" s="13"/>
     </row>
-    <row r="74" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:21" ht="117">
       <c r="A74" s="77">
         <f t="shared" si="37"/>
         <v>4</v>
@@ -12714,14 +12719,14 @@
         <v>300</v>
       </c>
       <c r="O74" s="26" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="P74" s="14"/>
       <c r="Q74" s="28"/>
       <c r="R74" s="15"/>
       <c r="U74" s="13"/>
     </row>
-    <row r="75" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:21" ht="136.5">
       <c r="A75" s="77">
         <f t="shared" si="37"/>
         <v>4</v>
@@ -12770,7 +12775,7 @@
         <v>303</v>
       </c>
       <c r="O75" s="26" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="P75" s="14"/>
       <c r="Q75" s="16" t="s">
@@ -12779,7 +12784,7 @@
       <c r="R75" s="14"/>
       <c r="U75" s="13"/>
     </row>
-    <row r="76" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:21" ht="136.5">
       <c r="A76" s="77">
         <f t="shared" si="37"/>
         <v>4</v>
@@ -12828,7 +12833,7 @@
         <v>307</v>
       </c>
       <c r="O76" s="26" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="P76" s="14"/>
       <c r="Q76" s="16" t="s">
@@ -12837,7 +12842,7 @@
       <c r="R76" s="14"/>
       <c r="U76" s="13"/>
     </row>
-    <row r="77" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:21" ht="136.5">
       <c r="A77" s="77">
         <f t="shared" ref="A77:D77" si="39">A76</f>
         <v>4</v>
@@ -12882,7 +12887,7 @@
         <v>314</v>
       </c>
       <c r="O77" s="26" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="P77" s="14"/>
       <c r="Q77" s="16" t="s">
@@ -12891,7 +12896,7 @@
       <c r="R77" s="14"/>
       <c r="U77" s="13"/>
     </row>
-    <row r="78" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:21" ht="136.5">
       <c r="A78" s="77">
         <f t="shared" ref="A78:G80" si="40">A77</f>
         <v>4</v>
@@ -12937,17 +12942,17 @@
       <c r="L78" s="40"/>
       <c r="M78" s="40"/>
       <c r="N78" s="26" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="O78" s="26" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="P78" s="14"/>
       <c r="Q78" s="28"/>
       <c r="R78" s="15"/>
       <c r="U78" s="13"/>
     </row>
-    <row r="79" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:21" ht="117">
       <c r="A79" s="77">
         <f t="shared" si="40"/>
         <v>4</v>
@@ -12998,7 +13003,7 @@
         <v>319</v>
       </c>
       <c r="O79" s="26" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="P79" s="14"/>
       <c r="Q79" s="16" t="s">
@@ -13007,7 +13012,7 @@
       <c r="R79" s="14"/>
       <c r="U79" s="13"/>
     </row>
-    <row r="80" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:21" ht="136.5">
       <c r="A80" s="77">
         <f t="shared" si="40"/>
         <v>4</v>
@@ -13056,7 +13061,7 @@
         <v>323</v>
       </c>
       <c r="O80" s="26" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="P80" s="14"/>
       <c r="Q80" s="16" t="s">
@@ -13065,7 +13070,7 @@
       <c r="R80" s="14"/>
       <c r="U80" s="13"/>
     </row>
-    <row r="81" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:21" ht="136.5">
       <c r="A81" s="77">
         <f t="shared" ref="A81:D81" si="42">A80</f>
         <v>4</v>
@@ -13110,7 +13115,7 @@
         <v>330</v>
       </c>
       <c r="O81" s="26" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="P81" s="14"/>
       <c r="Q81" s="16" t="s">
@@ -13119,7 +13124,7 @@
       <c r="R81" s="14"/>
       <c r="U81" s="13"/>
     </row>
-    <row r="82" spans="1:21" ht="253.5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="253.5">
       <c r="A82" s="77">
         <f t="shared" ref="A82:G82" si="43">A81</f>
         <v>4</v>
@@ -13174,14 +13179,14 @@
         <v>332</v>
       </c>
       <c r="O82" s="26" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="P82" s="14"/>
       <c r="Q82" s="28"/>
       <c r="R82" s="15"/>
       <c r="U82" s="13"/>
     </row>
-    <row r="83" spans="1:21" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:21" ht="175.5">
       <c r="A83" s="77">
         <f t="shared" ref="A83:D83" si="45">A82</f>
         <v>4</v>
@@ -13226,7 +13231,7 @@
         <v>338</v>
       </c>
       <c r="O83" s="26" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="P83" s="14"/>
       <c r="Q83" s="16" t="s">
@@ -13235,7 +13240,7 @@
       <c r="R83" s="14"/>
       <c r="U83" s="13"/>
     </row>
-    <row r="84" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:21" ht="136.5">
       <c r="A84" s="77">
         <f t="shared" ref="A84:G87" si="46">A83</f>
         <v>4</v>
@@ -13286,7 +13291,7 @@
         <v>340</v>
       </c>
       <c r="O84" s="26" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="16" t="s">
@@ -13295,7 +13300,7 @@
       <c r="R84" s="14"/>
       <c r="U84" s="13"/>
     </row>
-    <row r="85" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:21" ht="136.5">
       <c r="A85" s="77">
         <f t="shared" si="46"/>
         <v>4</v>
@@ -13344,7 +13349,7 @@
         <v>344</v>
       </c>
       <c r="O85" s="26" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="P85" s="14"/>
       <c r="Q85" s="16" t="s">
@@ -13353,7 +13358,7 @@
       <c r="R85" s="14"/>
       <c r="U85" s="13"/>
     </row>
-    <row r="86" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="97.5">
       <c r="A86" s="77">
         <f t="shared" si="46"/>
         <v>4</v>
@@ -13404,14 +13409,14 @@
         <v>346</v>
       </c>
       <c r="O86" s="26" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="P86" s="14"/>
       <c r="Q86" s="28"/>
       <c r="R86" s="15"/>
       <c r="U86" s="13"/>
     </row>
-    <row r="87" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:21" ht="136.5">
       <c r="A87" s="77">
         <f t="shared" si="46"/>
         <v>4</v>
@@ -13460,7 +13465,7 @@
         <v>349</v>
       </c>
       <c r="O87" s="26" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="P87" s="14"/>
       <c r="Q87" s="16" t="s">
@@ -13469,7 +13474,7 @@
       <c r="R87" s="14"/>
       <c r="U87" s="13"/>
     </row>
-    <row r="88" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:21" ht="136.5">
       <c r="A88" s="77">
         <f t="shared" ref="A88:D88" si="49">A87</f>
         <v>4</v>
@@ -13514,7 +13519,7 @@
         <v>356</v>
       </c>
       <c r="O88" s="26" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="P88" s="14"/>
       <c r="Q88" s="16" t="s">
@@ -13523,7 +13528,7 @@
       <c r="R88" s="14"/>
       <c r="U88" s="13"/>
     </row>
-    <row r="89" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:21" ht="97.5">
       <c r="A89" s="77">
         <f t="shared" ref="A89:G91" si="50">A88</f>
         <v>4</v>
@@ -13574,14 +13579,14 @@
         <v>358</v>
       </c>
       <c r="O89" s="26" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="P89" s="14"/>
       <c r="Q89" s="28"/>
       <c r="R89" s="15"/>
       <c r="U89" s="13"/>
     </row>
-    <row r="90" spans="1:21" ht="195" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:21" ht="195">
       <c r="A90" s="77">
         <f t="shared" si="50"/>
         <v>4</v>
@@ -13615,7 +13620,7 @@
         <v>★3</v>
       </c>
       <c r="I90" s="26" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="J90" s="26" t="s">
         <v>360</v>
@@ -13627,10 +13632,10 @@
       <c r="L90" s="14"/>
       <c r="M90" s="14"/>
       <c r="N90" s="26" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="O90" s="26" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="P90" s="14"/>
       <c r="Q90" s="16" t="s">
@@ -13639,7 +13644,7 @@
       <c r="R90" s="14"/>
       <c r="U90" s="13"/>
     </row>
-    <row r="91" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:21" ht="97.5">
       <c r="A91" s="77">
         <f t="shared" si="50"/>
         <v>4</v>
@@ -13688,7 +13693,7 @@
         <v>364</v>
       </c>
       <c r="O91" s="26" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="P91" s="14"/>
       <c r="Q91" s="16" t="s">
@@ -13697,7 +13702,7 @@
       <c r="R91" s="14"/>
       <c r="U91" s="13"/>
     </row>
-    <row r="92" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:21" ht="156">
       <c r="A92" s="77">
         <f t="shared" ref="A92:B92" si="52">A91</f>
         <v>4</v>
@@ -13740,7 +13745,7 @@
         <v>373</v>
       </c>
       <c r="O92" s="26" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="P92" s="14"/>
       <c r="Q92" s="16" t="s">
@@ -13749,7 +13754,7 @@
       <c r="R92" s="14"/>
       <c r="U92" s="13"/>
     </row>
-    <row r="93" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:21" ht="117">
       <c r="A93" s="77">
         <f t="shared" ref="A93:G94" si="53">A92</f>
         <v>4</v>
@@ -13798,16 +13803,16 @@
         <v>377</v>
       </c>
       <c r="O93" s="26" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="P93" s="14"/>
       <c r="Q93" s="16" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="R93" s="14"/>
       <c r="U93" s="13"/>
     </row>
-    <row r="94" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:21" ht="117">
       <c r="A94" s="77">
         <f t="shared" si="53"/>
         <v>4</v>
@@ -13856,7 +13861,7 @@
         <v>380</v>
       </c>
       <c r="O94" s="26" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="P94" s="14"/>
       <c r="Q94" s="16" t="s">
@@ -13865,7 +13870,7 @@
       <c r="R94" s="14"/>
       <c r="U94" s="13"/>
     </row>
-    <row r="95" spans="1:21" ht="234" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:21" ht="234">
       <c r="A95" s="77">
         <f t="shared" ref="A95:D95" si="55">A94</f>
         <v>4</v>
@@ -13898,7 +13903,7 @@
         <v>385</v>
       </c>
       <c r="J95" s="26" t="s">
-        <v>920</v>
+        <v>1203</v>
       </c>
       <c r="K95" s="26" t="str">
         <f t="shared" si="48"/>
@@ -13910,7 +13915,7 @@
         <v>386</v>
       </c>
       <c r="O95" s="26" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="P95" s="14"/>
       <c r="Q95" s="27" t="s">
@@ -13919,7 +13924,7 @@
       <c r="R95" s="14"/>
       <c r="U95" s="13"/>
     </row>
-    <row r="96" spans="1:21" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:21" ht="351">
       <c r="A96" s="77">
         <f t="shared" ref="A96:G99" si="56">A95</f>
         <v>4</v>
@@ -13944,7 +13949,7 @@
         <f t="shared" si="56"/>
         <v>セキュリティパッチ・アップデートの手続</v>
       </c>
-      <c r="G96" s="26" t="str">
+      <c r="G96" s="91" t="str">
         <f t="shared" si="56"/>
         <v>情報機器、OS及びソフトウェアへのセキュリティパッチ及びアップデートの適用に係る手続を定めること。</v>
       </c>
@@ -13968,7 +13973,7 @@
         <v>390</v>
       </c>
       <c r="O96" s="26" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="P96" s="14"/>
       <c r="Q96" s="27" t="s">
@@ -13977,7 +13982,7 @@
       <c r="R96" s="14"/>
       <c r="U96" s="13"/>
     </row>
-    <row r="97" spans="1:21" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:21" ht="117">
       <c r="A97" s="77">
         <f t="shared" si="56"/>
         <v>4</v>
@@ -13998,23 +14003,23 @@
         <f t="shared" si="56"/>
         <v>4-4-4</v>
       </c>
-      <c r="F97" s="26" t="str">
+      <c r="F97" s="88" t="str">
         <f t="shared" si="56"/>
         <v>セキュリティパッチ・アップデートの手続</v>
       </c>
-      <c r="G97" s="26" t="str">
+      <c r="G97" s="88" t="str">
         <f t="shared" si="56"/>
         <v>情報機器、OS及びソフトウェアへのセキュリティパッチ及びアップデートの適用に係る手続を定めること。</v>
       </c>
-      <c r="H97" s="26" t="str">
+      <c r="H97" s="88" t="str">
         <f t="shared" ref="H97:I99" si="57">H96</f>
         <v>★3</v>
       </c>
-      <c r="I97" s="26" t="str">
+      <c r="I97" s="88" t="str">
         <f t="shared" si="57"/>
         <v>4-4-4-2</v>
       </c>
-      <c r="J97" s="26" t="str">
+      <c r="J97" s="88" t="str">
         <f t="shared" ref="J97:J99" si="58">J96</f>
         <v>・利用している機能又は設定に関して、以下のいずれかに該当するアップデートプログラムがリリースされてから14日以内に、アップデートすること。
 - 当該アップデートが、ベンダーにより「重大」(Critical)又は 「高リスク」(High Risk)と説明される脆弱性を修正するものである。
@@ -14027,7 +14032,7 @@
 -会社支給のスマートデバイスのOS及びアプリ 
 -インターネットとの境界に設置されているネットワーク機器のOS及びファームウェア</v>
       </c>
-      <c r="K97" s="26" t="str">
+      <c r="K97" s="88" t="str">
         <f t="shared" si="48"/>
         <v>防御(PR)</v>
       </c>
@@ -14037,7 +14042,7 @@
         <v>392</v>
       </c>
       <c r="O97" s="26" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="P97" s="14"/>
       <c r="Q97" s="27" t="s">
@@ -14046,7 +14051,7 @@
       <c r="R97" s="14"/>
       <c r="U97" s="13"/>
     </row>
-    <row r="98" spans="1:21" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:21" ht="171">
       <c r="A98" s="77">
         <f t="shared" si="56"/>
         <v>4</v>
@@ -14067,23 +14072,23 @@
         <f t="shared" si="56"/>
         <v>4-4-4</v>
       </c>
-      <c r="F98" s="26" t="str">
+      <c r="F98" s="88" t="str">
         <f t="shared" si="56"/>
         <v>セキュリティパッチ・アップデートの手続</v>
       </c>
-      <c r="G98" s="26" t="str">
+      <c r="G98" s="88" t="str">
         <f t="shared" si="56"/>
         <v>情報機器、OS及びソフトウェアへのセキュリティパッチ及びアップデートの適用に係る手続を定めること。</v>
       </c>
-      <c r="H98" s="26" t="str">
+      <c r="H98" s="88" t="str">
         <f t="shared" si="57"/>
         <v>★3</v>
       </c>
-      <c r="I98" s="26" t="str">
+      <c r="I98" s="88" t="str">
         <f t="shared" si="57"/>
         <v>4-4-4-2</v>
       </c>
-      <c r="J98" s="26" t="str">
+      <c r="J98" s="89" t="str">
         <f t="shared" si="58"/>
         <v>・利用している機能又は設定に関して、以下のいずれかに該当するアップデートプログラムがリリースされてから14日以内に、アップデートすること。
 - 当該アップデートが、ベンダーにより「重大」(Critical)又は 「高リスク」(High Risk)と説明される脆弱性を修正するものである。
@@ -14096,7 +14101,7 @@
 -会社支給のスマートデバイスのOS及びアプリ 
 -インターネットとの境界に設置されているネットワーク機器のOS及びファームウェア</v>
       </c>
-      <c r="K98" s="26" t="str">
+      <c r="K98" s="88" t="str">
         <f t="shared" si="48"/>
         <v>防御(PR)</v>
       </c>
@@ -14106,7 +14111,7 @@
         <v>394</v>
       </c>
       <c r="O98" s="26" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="27" t="s">
@@ -14115,7 +14120,7 @@
       <c r="R98" s="14"/>
       <c r="U98" s="13"/>
     </row>
-    <row r="99" spans="1:21" ht="409.5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:21" ht="409.5">
       <c r="A99" s="77">
         <f t="shared" si="56"/>
         <v>4</v>
@@ -14136,23 +14141,23 @@
         <f t="shared" si="56"/>
         <v>4-4-4</v>
       </c>
-      <c r="F99" s="26" t="str">
+      <c r="F99" s="88" t="str">
         <f t="shared" si="56"/>
         <v>セキュリティパッチ・アップデートの手続</v>
       </c>
-      <c r="G99" s="26" t="str">
+      <c r="G99" s="88" t="str">
         <f t="shared" si="56"/>
         <v>情報機器、OS及びソフトウェアへのセキュリティパッチ及びアップデートの適用に係る手続を定めること。</v>
       </c>
-      <c r="H99" s="26" t="str">
+      <c r="H99" s="88" t="str">
         <f t="shared" si="57"/>
         <v>★3</v>
       </c>
-      <c r="I99" s="26" t="str">
+      <c r="I99" s="88" t="str">
         <f t="shared" si="57"/>
         <v>4-4-4-2</v>
       </c>
-      <c r="J99" s="26" t="str">
+      <c r="J99" s="90" t="str">
         <f t="shared" si="58"/>
         <v>・利用している機能又は設定に関して、以下のいずれかに該当するアップデートプログラムがリリースされてから14日以内に、アップデートすること。
 - 当該アップデートが、ベンダーにより「重大」(Critical)又は 「高リスク」(High Risk)と説明される脆弱性を修正するものである。
@@ -14165,26 +14170,26 @@
 -会社支給のスマートデバイスのOS及びアプリ 
 -インターネットとの境界に設置されているネットワーク機器のOS及びファームウェア</v>
       </c>
-      <c r="K99" s="26" t="str">
+      <c r="K99" s="88" t="str">
         <f t="shared" si="48"/>
         <v>防御(PR)</v>
       </c>
       <c r="L99" s="40"/>
       <c r="M99" s="40"/>
       <c r="N99" s="26" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="O99" s="26" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="P99" s="14"/>
       <c r="Q99" s="27" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="R99" s="14"/>
       <c r="U99" s="13"/>
     </row>
-    <row r="100" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:21" ht="136.5">
       <c r="A100" s="78">
         <f t="shared" ref="A100:D100" si="59">A99</f>
         <v>4</v>
@@ -14229,7 +14234,7 @@
         <v>401</v>
       </c>
       <c r="O100" s="26" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="P100" s="14"/>
       <c r="Q100" s="16" t="s">
@@ -14238,7 +14243,7 @@
       <c r="R100" s="14"/>
       <c r="U100" s="13"/>
     </row>
-    <row r="101" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:21" ht="117">
       <c r="A101" s="78">
         <f t="shared" ref="A101:G103" si="60">A100</f>
         <v>4</v>
@@ -14287,7 +14292,7 @@
         <v>405</v>
       </c>
       <c r="O101" s="26" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="P101" s="14"/>
       <c r="Q101" s="16" t="s">
@@ -14296,7 +14301,7 @@
       <c r="R101" s="14"/>
       <c r="U101" s="13"/>
     </row>
-    <row r="102" spans="1:21" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:21" ht="175.5">
       <c r="A102" s="78">
         <f t="shared" si="60"/>
         <v>4</v>
@@ -14344,17 +14349,17 @@
       <c r="L102" s="40"/>
       <c r="M102" s="40"/>
       <c r="N102" s="26" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="O102" s="26" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="P102" s="14"/>
       <c r="Q102" s="28"/>
       <c r="R102" s="15"/>
       <c r="U102" s="13"/>
     </row>
-    <row r="103" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:21" ht="136.5">
       <c r="A103" s="78">
         <f t="shared" si="60"/>
         <v>4</v>
@@ -14403,7 +14408,7 @@
         <v>409</v>
       </c>
       <c r="O103" s="26" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="P103" s="14"/>
       <c r="Q103" s="16" t="s">
@@ -14412,7 +14417,7 @@
       <c r="R103" s="14"/>
       <c r="U103" s="13"/>
     </row>
-    <row r="104" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:21" ht="156">
       <c r="A104" s="77">
         <f t="shared" ref="A104:B104" si="62">A103</f>
         <v>4</v>
@@ -14455,7 +14460,7 @@
         <v>418</v>
       </c>
       <c r="O104" s="26" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="P104" s="14"/>
       <c r="Q104" s="16" t="s">
@@ -14464,7 +14469,7 @@
       <c r="R104" s="14"/>
       <c r="U104" s="13"/>
     </row>
-    <row r="105" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:21" ht="136.5">
       <c r="A105" s="77">
         <f t="shared" ref="A105:G110" si="63">A104</f>
         <v>4</v>
@@ -14513,7 +14518,7 @@
         <v>422</v>
       </c>
       <c r="O105" s="26" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="P105" s="14"/>
       <c r="Q105" s="27" t="s">
@@ -14522,7 +14527,7 @@
       <c r="R105" s="14"/>
       <c r="U105" s="13"/>
     </row>
-    <row r="106" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:21" ht="136.5">
       <c r="A106" s="77">
         <f t="shared" si="63"/>
         <v>4</v>
@@ -14571,7 +14576,7 @@
         <v>426</v>
       </c>
       <c r="O106" s="26" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="P106" s="14"/>
       <c r="Q106" s="16" t="s">
@@ -14580,7 +14585,7 @@
       <c r="R106" s="14"/>
       <c r="U106" s="13"/>
     </row>
-    <row r="107" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:21" ht="136.5">
       <c r="A107" s="77">
         <f t="shared" si="63"/>
         <v>4</v>
@@ -14629,7 +14634,7 @@
         <v>430</v>
       </c>
       <c r="O107" s="26" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="P107" s="14"/>
       <c r="Q107" s="16" t="s">
@@ -14638,7 +14643,7 @@
       <c r="R107" s="14"/>
       <c r="U107" s="13"/>
     </row>
-    <row r="108" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:21" ht="156">
       <c r="A108" s="77">
         <f t="shared" si="63"/>
         <v>4</v>
@@ -14687,7 +14692,7 @@
         <v>434</v>
       </c>
       <c r="O108" s="26" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="P108" s="14"/>
       <c r="Q108" s="27" t="s">
@@ -14696,7 +14701,7 @@
       <c r="R108" s="14"/>
       <c r="U108" s="13"/>
     </row>
-    <row r="109" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:21" ht="136.5">
       <c r="A109" s="77">
         <f t="shared" si="63"/>
         <v>4</v>
@@ -14745,7 +14750,7 @@
         <v>438</v>
       </c>
       <c r="O109" s="26" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="P109" s="14"/>
       <c r="Q109" s="16" t="s">
@@ -14754,7 +14759,7 @@
       <c r="R109" s="14"/>
       <c r="U109" s="13"/>
     </row>
-    <row r="110" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:21" ht="156">
       <c r="A110" s="77">
         <f t="shared" si="63"/>
         <v>4</v>
@@ -14803,7 +14808,7 @@
         <v>442</v>
       </c>
       <c r="O110" s="26" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="P110" s="14"/>
       <c r="Q110" s="16" t="s">
@@ -14812,7 +14817,7 @@
       <c r="R110" s="14"/>
       <c r="U110" s="13"/>
     </row>
-    <row r="111" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:21" ht="156">
       <c r="A111" s="44">
         <v>5</v>
       </c>
@@ -14852,7 +14857,7 @@
         <v>453</v>
       </c>
       <c r="O111" s="26" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="P111" s="14"/>
       <c r="Q111" s="16" t="s">
@@ -14861,7 +14866,7 @@
       <c r="R111" s="14"/>
       <c r="U111" s="13"/>
     </row>
-    <row r="112" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:21" ht="117">
       <c r="A112" s="76">
         <f t="shared" ref="A112:G115" si="65">A111</f>
         <v>5</v>
@@ -14910,14 +14915,14 @@
         <v>457</v>
       </c>
       <c r="O112" s="26" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="28"/>
       <c r="R112" s="15"/>
       <c r="U112" s="13"/>
     </row>
-    <row r="113" spans="1:21" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:21" ht="175.5">
       <c r="A113" s="76">
         <f t="shared" si="65"/>
         <v>5</v>
@@ -14968,7 +14973,7 @@
         <v>458</v>
       </c>
       <c r="O113" s="26" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="P113" s="14"/>
       <c r="Q113" s="16" t="s">
@@ -14977,7 +14982,7 @@
       <c r="R113" s="14"/>
       <c r="U113" s="13"/>
     </row>
-    <row r="114" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:21" ht="136.5">
       <c r="A114" s="76">
         <f t="shared" si="65"/>
         <v>5</v>
@@ -15028,7 +15033,7 @@
         <v>460</v>
       </c>
       <c r="O114" s="26" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="P114" s="14"/>
       <c r="Q114" s="16" t="s">
@@ -15037,7 +15042,7 @@
       <c r="R114" s="14"/>
       <c r="U114" s="13"/>
     </row>
-    <row r="115" spans="1:21" ht="156" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:21" ht="156">
       <c r="A115" s="76">
         <f t="shared" si="65"/>
         <v>5</v>
@@ -15086,7 +15091,7 @@
         <v>464</v>
       </c>
       <c r="O115" s="26" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="P115" s="14"/>
       <c r="Q115" s="16" t="s">
@@ -15095,7 +15100,7 @@
       <c r="R115" s="14"/>
       <c r="U115" s="13"/>
     </row>
-    <row r="116" spans="1:21" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:21" ht="97.5">
       <c r="A116" s="45">
         <v>6</v>
       </c>
@@ -15135,7 +15140,7 @@
         <v>475</v>
       </c>
       <c r="O116" s="26" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="P116" s="14"/>
       <c r="Q116" s="16" t="s">
@@ -15144,7 +15149,7 @@
       <c r="R116" s="14"/>
       <c r="U116" s="13"/>
     </row>
-    <row r="117" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:21" ht="117">
       <c r="A117" s="75">
         <f t="shared" ref="A117:G124" si="70">A116</f>
         <v>6</v>
@@ -15197,14 +15202,14 @@
         <v>477</v>
       </c>
       <c r="O117" s="26" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="P117" s="14"/>
       <c r="Q117" s="28"/>
       <c r="R117" s="15"/>
       <c r="U117" s="13"/>
     </row>
-    <row r="118" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:21" ht="136.5">
       <c r="A118" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15253,7 +15258,7 @@
         <v>480</v>
       </c>
       <c r="O118" s="26" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="P118" s="14"/>
       <c r="Q118" s="16" t="s">
@@ -15262,7 +15267,7 @@
       <c r="R118" s="14"/>
       <c r="U118" s="13"/>
     </row>
-    <row r="119" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:21" ht="117">
       <c r="A119" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15313,14 +15318,14 @@
         <v>482</v>
       </c>
       <c r="O119" s="26" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="28"/>
       <c r="R119" s="15"/>
       <c r="U119" s="13"/>
     </row>
-    <row r="120" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:21" ht="136.5">
       <c r="A120" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15369,7 +15374,7 @@
         <v>485</v>
       </c>
       <c r="O120" s="26" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="P120" s="14"/>
       <c r="Q120" s="16" t="s">
@@ -15378,7 +15383,7 @@
       <c r="R120" s="14"/>
       <c r="U120" s="13"/>
     </row>
-    <row r="121" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:21" ht="117">
       <c r="A121" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15427,7 +15432,7 @@
         <v>489</v>
       </c>
       <c r="O121" s="26" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="P121" s="14"/>
       <c r="Q121" s="27" t="s">
@@ -15436,7 +15441,7 @@
       <c r="R121" s="14"/>
       <c r="U121" s="13"/>
     </row>
-    <row r="122" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:21" ht="117">
       <c r="A122" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15485,7 +15490,7 @@
         <v>493</v>
       </c>
       <c r="O122" s="26" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="P122" s="14"/>
       <c r="Q122" s="16" t="s">
@@ -15494,7 +15499,7 @@
       <c r="R122" s="14"/>
       <c r="U122" s="13"/>
     </row>
-    <row r="123" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:21" ht="136.5">
       <c r="A123" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15543,7 +15548,7 @@
         <v>497</v>
       </c>
       <c r="O123" s="26" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="P123" s="14"/>
       <c r="Q123" s="16" t="s">
@@ -15552,7 +15557,7 @@
       <c r="R123" s="14"/>
       <c r="U123" s="13"/>
     </row>
-    <row r="124" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:21" ht="136.5">
       <c r="A124" s="75">
         <f t="shared" si="70"/>
         <v>6</v>
@@ -15603,7 +15608,7 @@
         <v>499</v>
       </c>
       <c r="O124" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="P124" s="14"/>
       <c r="Q124" s="16" t="s">
@@ -15612,7 +15617,7 @@
       <c r="R124" s="14"/>
       <c r="U124" s="13"/>
     </row>
-    <row r="125" spans="1:21" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:21" ht="136.5">
       <c r="A125" s="46">
         <v>7</v>
       </c>
@@ -15652,7 +15657,7 @@
         <v>510</v>
       </c>
       <c r="O125" s="26" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="P125" s="14"/>
       <c r="Q125" s="27" t="s">
@@ -15661,7 +15666,7 @@
       <c r="R125" s="14"/>
       <c r="U125" s="13"/>
     </row>
-    <row r="126" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:21" ht="117">
       <c r="A126" s="74">
         <f t="shared" ref="A126:G126" si="75">A125</f>
         <v>7</v>
@@ -15715,7 +15720,7 @@
         <v>512</v>
       </c>
       <c r="O126" s="26" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="P126" s="14"/>
       <c r="Q126" s="27" t="s">
@@ -15724,37 +15729,37 @@
       <c r="R126" s="14"/>
       <c r="U126" s="13"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:21">
       <c r="K127" s="13"/>
       <c r="M127" s="12"/>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:21">
       <c r="H128" s="13"/>
       <c r="I128" s="13"/>
       <c r="J128" s="13"/>
       <c r="K128" s="13"/>
       <c r="M128" s="12"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:18">
       <c r="H129" s="13"/>
       <c r="I129" s="13"/>
       <c r="J129" s="13"/>
       <c r="K129" s="13"/>
       <c r="M129" s="12"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:18">
       <c r="K130" s="13"/>
       <c r="M130" s="12"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:18">
       <c r="K131" s="13"/>
       <c r="M131" s="12"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:18">
       <c r="K132" s="13"/>
       <c r="M132" s="12"/>
     </row>
-    <row r="133" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:18" s="13" customFormat="1">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -15773,7 +15778,7 @@
       <c r="Q133" s="12"/>
       <c r="R133" s="12"/>
     </row>
-    <row r="134" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:18" s="13" customFormat="1">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -15839,7 +15844,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LSCS-410AP ★3・★4 自己評価等ガイド 別紙_アセスメントシート（Ver1.0：2026年10月28日）&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
@@ -15867,7 +15872,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U240"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="19.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="12" customWidth="1" outlineLevel="1"/>
     <col min="2" max="2" width="12.25" style="12" customWidth="1" outlineLevel="1"/>
@@ -15892,7 +15897,7 @@
     <col min="22" max="16384" width="8.625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21">
       <c r="K1" s="13"/>
       <c r="M1" s="12"/>
       <c r="O1" s="81" t="s">
@@ -15902,7 +15907,7 @@
       <c r="Q1" s="82"/>
       <c r="R1" s="82"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21">
       <c r="K2" s="13"/>
       <c r="M2" s="12"/>
       <c r="O2" s="34" t="s">
@@ -15912,7 +15917,7 @@
       <c r="Q2" s="55"/>
       <c r="R2" s="48"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21">
       <c r="K3" s="13"/>
       <c r="M3" s="12"/>
       <c r="O3" s="36" t="s">
@@ -15922,7 +15927,7 @@
       <c r="Q3" s="56"/>
       <c r="R3" s="50"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21">
       <c r="K4" s="13"/>
       <c r="M4" s="12"/>
       <c r="O4" s="36" t="s">
@@ -15932,7 +15937,7 @@
       <c r="Q4" s="56"/>
       <c r="R4" s="50"/>
     </row>
-    <row r="5" spans="1:21" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" ht="20.25" thickBot="1">
       <c r="K5" s="13"/>
       <c r="M5" s="12"/>
       <c r="O5" s="83" t="s">
@@ -15942,67 +15947,67 @@
       <c r="Q5" s="57"/>
       <c r="R5" s="52"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21">
       <c r="K6" s="13"/>
       <c r="M6" s="12"/>
       <c r="O6" s="84" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="P6" s="85"/>
       <c r="Q6" s="85"/>
       <c r="R6" s="86"/>
     </row>
-    <row r="7" spans="1:21" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" ht="58.5">
       <c r="K7" s="13"/>
       <c r="M7" s="12"/>
       <c r="O7" s="34" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="P7" s="47"/>
       <c r="Q7" s="55"/>
       <c r="R7" s="48"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21">
       <c r="K8" s="13"/>
       <c r="M8" s="12"/>
       <c r="O8" s="36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="P8" s="49"/>
       <c r="Q8" s="56"/>
       <c r="R8" s="50"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21">
       <c r="K9" s="13"/>
       <c r="M9" s="12"/>
       <c r="O9" s="36" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="P9" s="49"/>
       <c r="Q9" s="56"/>
       <c r="R9" s="50"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21">
       <c r="K10" s="13"/>
       <c r="M10" s="12"/>
       <c r="O10" s="36" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="P10" s="59"/>
       <c r="Q10" s="60"/>
       <c r="R10" s="61"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21">
       <c r="K11" s="13"/>
       <c r="M11" s="12"/>
       <c r="O11" s="36" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="P11" s="49"/>
       <c r="Q11" s="56"/>
       <c r="R11" s="50"/>
     </row>
-    <row r="12" spans="1:21" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" ht="20.25" thickBot="1">
       <c r="K12" s="13"/>
       <c r="M12" s="12"/>
       <c r="O12" s="39" t="s">
@@ -16012,7 +16017,7 @@
       <c r="Q12" s="58"/>
       <c r="R12" s="54"/>
     </row>
-    <row r="13" spans="1:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="24">
       <c r="A13" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.TEXTAFTER(CELL("filename",A1),"]")</f>
         <v>【★4用】アセスメントシート</v>
@@ -16022,7 +16027,7 @@
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" spans="1:21" s="29" customFormat="1" ht="78" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" s="29" customFormat="1" ht="78">
       <c r="A14" s="18" t="s">
         <v>38</v>
       </c>
@@ -16057,16 +16062,16 @@
         <v>50</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="M14" s="20" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="N14" s="21" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="P14" s="22" t="s">
         <v>51</v>
@@ -16079,7 +16084,7 @@
       </c>
       <c r="U14" s="30"/>
     </row>
-    <row r="15" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" ht="117">
       <c r="A15" s="25">
         <v>1</v>
       </c>
@@ -16119,7 +16124,7 @@
         <v>522</v>
       </c>
       <c r="O15" s="26" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="P15" s="14"/>
       <c r="Q15" s="16" t="s">
@@ -16127,7 +16132,7 @@
       </c>
       <c r="R15" s="14"/>
     </row>
-    <row r="16" spans="1:21" ht="117" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" ht="117">
       <c r="A16" s="80">
         <f t="shared" ref="A16:G19" si="0">A15</f>
         <v>1</v>
@@ -16181,13 +16186,13 @@
         <v>524</v>
       </c>
       <c r="O16" s="26" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="P16" s="14"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="15"/>
     </row>
-    <row r="17" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:18" ht="156">
       <c r="A17" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -16236,7 +16241,7 @@
         <v>527</v>
       </c>
       <c r="O17" s="26" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="P17" s="14"/>
       <c r="Q17" s="16" t="s">
@@ -16244,7 +16249,7 @@
       </c>
       <c r="R17" s="14"/>
     </row>
-    <row r="18" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:18" ht="97.5">
       <c r="A18" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -16295,13 +16300,13 @@
         <v>529</v>
       </c>
       <c r="O18" s="26" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="P18" s="14"/>
       <c r="Q18" s="28"/>
       <c r="R18" s="15"/>
     </row>
-    <row r="19" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:18" ht="156">
       <c r="A19" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -16350,7 +16355,7 @@
         <v>532</v>
       </c>
       <c r="O19" s="26" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="P19" s="14"/>
       <c r="Q19" s="16" t="s">
@@ -16358,7 +16363,7 @@
       </c>
       <c r="R19" s="14"/>
     </row>
-    <row r="20" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:18" ht="136.5">
       <c r="A20" s="80">
         <f t="shared" ref="A20:B20" si="3">A19</f>
         <v>1</v>
@@ -16401,7 +16406,7 @@
         <v>64</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="P20" s="14"/>
       <c r="Q20" s="16" t="s">
@@ -16409,7 +16414,7 @@
       </c>
       <c r="R20" s="14"/>
     </row>
-    <row r="21" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:18" ht="175.5">
       <c r="A21" s="80">
         <f t="shared" ref="A21:G24" si="4">A20</f>
         <v>1</v>
@@ -16460,13 +16465,13 @@
         <v>66</v>
       </c>
       <c r="O21" s="26" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="P21" s="14"/>
       <c r="Q21" s="28"/>
       <c r="R21" s="15"/>
     </row>
-    <row r="22" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:18" ht="156">
       <c r="A22" s="80">
         <f t="shared" si="4"/>
         <v>1</v>
@@ -16515,7 +16520,7 @@
         <v>69</v>
       </c>
       <c r="O22" s="26" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="P22" s="14"/>
       <c r="Q22" s="16" t="s">
@@ -16523,7 +16528,7 @@
       </c>
       <c r="R22" s="14"/>
     </row>
-    <row r="23" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:18" ht="117">
       <c r="A23" s="80">
         <f t="shared" si="4"/>
         <v>1</v>
@@ -16572,7 +16577,7 @@
         <v>73</v>
       </c>
       <c r="O23" s="26" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="P23" s="14"/>
       <c r="Q23" s="27" t="s">
@@ -16580,7 +16585,7 @@
       </c>
       <c r="R23" s="14"/>
     </row>
-    <row r="24" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:18" ht="195">
       <c r="A24" s="80">
         <f t="shared" si="4"/>
         <v>1</v>
@@ -16613,7 +16618,7 @@
         <v>44</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>534</v>
@@ -16628,7 +16633,7 @@
         <v>535</v>
       </c>
       <c r="O24" s="26" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="P24" s="14"/>
       <c r="Q24" s="16" t="s">
@@ -16636,7 +16641,7 @@
       </c>
       <c r="R24" s="14"/>
     </row>
-    <row r="25" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:18" ht="117">
       <c r="A25" s="80">
         <f t="shared" ref="A25:D25" si="6">A24</f>
         <v>1</v>
@@ -16681,7 +16686,7 @@
         <v>542</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="P25" s="14"/>
       <c r="Q25" s="16" t="s">
@@ -16689,7 +16694,7 @@
       </c>
       <c r="R25" s="14"/>
     </row>
-    <row r="26" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:18" ht="156">
       <c r="A26" s="80">
         <f t="shared" ref="A26:G28" si="7">A25</f>
         <v>1</v>
@@ -16740,7 +16745,7 @@
         <v>544</v>
       </c>
       <c r="O26" s="26" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="P26" s="14"/>
       <c r="Q26" s="16" t="s">
@@ -16748,7 +16753,7 @@
       </c>
       <c r="R26" s="14"/>
     </row>
-    <row r="27" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:18" ht="136.5">
       <c r="A27" s="80">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -16797,7 +16802,7 @@
         <v>548</v>
       </c>
       <c r="O27" s="26" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="P27" s="14"/>
       <c r="Q27" s="16" t="s">
@@ -16805,7 +16810,7 @@
       </c>
       <c r="R27" s="14"/>
     </row>
-    <row r="28" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:18" ht="136.5">
       <c r="A28" s="80">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -16856,7 +16861,7 @@
         <v>550</v>
       </c>
       <c r="O28" s="26" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="P28" s="14"/>
       <c r="Q28" s="16" t="s">
@@ -16864,7 +16869,7 @@
       </c>
       <c r="R28" s="14"/>
     </row>
-    <row r="29" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:18" ht="136.5">
       <c r="A29" s="80">
         <f t="shared" ref="A29:D29" si="9">A28</f>
         <v>1</v>
@@ -16909,7 +16914,7 @@
         <v>80</v>
       </c>
       <c r="O29" s="26" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="P29" s="14"/>
       <c r="Q29" s="16" t="s">
@@ -16917,7 +16922,7 @@
       </c>
       <c r="R29" s="14"/>
     </row>
-    <row r="30" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:18" ht="117">
       <c r="A30" s="80">
         <f t="shared" ref="A30:G33" si="10">A29</f>
         <v>1</v>
@@ -16966,7 +16971,7 @@
         <v>84</v>
       </c>
       <c r="O30" s="26" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="P30" s="14"/>
       <c r="Q30" s="16" t="s">
@@ -16974,7 +16979,7 @@
       </c>
       <c r="R30" s="14"/>
     </row>
-    <row r="31" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:18" ht="156">
       <c r="A31" s="80">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -17022,7 +17027,7 @@
         <v>554</v>
       </c>
       <c r="O31" s="26" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="P31" s="14"/>
       <c r="Q31" s="16" t="s">
@@ -17030,7 +17035,7 @@
       </c>
       <c r="R31" s="14"/>
     </row>
-    <row r="32" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:18" ht="117">
       <c r="A32" s="80">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -17082,13 +17087,13 @@
         <v>556</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="P32" s="14"/>
       <c r="Q32" s="28"/>
       <c r="R32" s="15"/>
     </row>
-    <row r="33" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:18" ht="156">
       <c r="A33" s="80">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -17137,7 +17142,7 @@
         <v>559</v>
       </c>
       <c r="O33" s="26" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="P33" s="14"/>
       <c r="Q33" s="16" t="s">
@@ -17145,7 +17150,7 @@
       </c>
       <c r="R33" s="14"/>
     </row>
-    <row r="34" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:18" ht="117">
       <c r="A34" s="80">
         <f t="shared" ref="A34:B34" si="12">A33</f>
         <v>1</v>
@@ -17188,7 +17193,7 @@
         <v>93</v>
       </c>
       <c r="O34" s="26" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="P34" s="14"/>
       <c r="Q34" s="16" t="s">
@@ -17196,7 +17201,7 @@
       </c>
       <c r="R34" s="14"/>
     </row>
-    <row r="35" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:18" ht="156">
       <c r="A35" s="80">
         <f t="shared" ref="A35:G37" si="13">A34</f>
         <v>1</v>
@@ -17245,7 +17250,7 @@
         <v>97</v>
       </c>
       <c r="O35" s="26" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="P35" s="14"/>
       <c r="Q35" s="16" t="s">
@@ -17253,7 +17258,7 @@
       </c>
       <c r="R35" s="14"/>
     </row>
-    <row r="36" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:18" ht="175.5">
       <c r="A36" s="80">
         <f t="shared" si="13"/>
         <v>1</v>
@@ -17302,7 +17307,7 @@
         <v>101</v>
       </c>
       <c r="O36" s="26" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="P36" s="14"/>
       <c r="Q36" s="16" t="s">
@@ -17310,7 +17315,7 @@
       </c>
       <c r="R36" s="14"/>
     </row>
-    <row r="37" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:18" ht="117">
       <c r="A37" s="80">
         <f t="shared" si="13"/>
         <v>1</v>
@@ -17358,7 +17363,7 @@
         <v>563</v>
       </c>
       <c r="O37" s="26" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="P37" s="14"/>
       <c r="Q37" s="16" t="s">
@@ -17366,7 +17371,7 @@
       </c>
       <c r="R37" s="14"/>
     </row>
-    <row r="38" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:18" ht="156">
       <c r="A38" s="80">
         <f t="shared" ref="A38:B38" si="15">A37</f>
         <v>1</v>
@@ -17409,7 +17414,7 @@
         <v>572</v>
       </c>
       <c r="O38" s="26" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="P38" s="14"/>
       <c r="Q38" s="27" t="s">
@@ -17417,7 +17422,7 @@
       </c>
       <c r="R38" s="14"/>
     </row>
-    <row r="39" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:18" ht="156">
       <c r="A39" s="80">
         <f t="shared" ref="A39:G44" si="16">A38</f>
         <v>1</v>
@@ -17470,13 +17475,13 @@
         <v>574</v>
       </c>
       <c r="O39" s="26" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="P39" s="14"/>
       <c r="Q39" s="28"/>
       <c r="R39" s="15"/>
     </row>
-    <row r="40" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:18" ht="175.5">
       <c r="A40" s="80">
         <f t="shared" si="16"/>
         <v>1</v>
@@ -17529,13 +17534,13 @@
         <v>575</v>
       </c>
       <c r="O40" s="26" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="P40" s="14"/>
       <c r="Q40" s="28"/>
       <c r="R40" s="15"/>
     </row>
-    <row r="41" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:18" ht="156">
       <c r="A41" s="80">
         <f t="shared" si="16"/>
         <v>1</v>
@@ -17588,13 +17593,13 @@
         <v>576</v>
       </c>
       <c r="O41" s="26" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="P41" s="14"/>
       <c r="Q41" s="28"/>
       <c r="R41" s="15"/>
     </row>
-    <row r="42" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:18" ht="175.5">
       <c r="A42" s="80">
         <f t="shared" si="16"/>
         <v>1</v>
@@ -17643,7 +17648,7 @@
         <v>579</v>
       </c>
       <c r="O42" s="26" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="27" t="s">
@@ -17651,7 +17656,7 @@
       </c>
       <c r="R42" s="14"/>
     </row>
-    <row r="43" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:18" ht="117">
       <c r="A43" s="80">
         <f t="shared" si="16"/>
         <v>1</v>
@@ -17702,13 +17707,13 @@
         <v>581</v>
       </c>
       <c r="O43" s="26" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="P43" s="14"/>
       <c r="Q43" s="28"/>
       <c r="R43" s="15"/>
     </row>
-    <row r="44" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:18" ht="117">
       <c r="A44" s="80">
         <f t="shared" si="16"/>
         <v>1</v>
@@ -17759,7 +17764,7 @@
         <v>582</v>
       </c>
       <c r="O44" s="26" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="P44" s="14"/>
       <c r="Q44" s="27" t="s">
@@ -17767,7 +17772,7 @@
       </c>
       <c r="R44" s="14"/>
     </row>
-    <row r="45" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:18" ht="136.5">
       <c r="A45" s="25">
         <v>2</v>
       </c>
@@ -17808,7 +17813,7 @@
         <v>111</v>
       </c>
       <c r="O45" s="26" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="P45" s="14"/>
       <c r="Q45" s="16" t="s">
@@ -17816,7 +17821,7 @@
       </c>
       <c r="R45" s="14"/>
     </row>
-    <row r="46" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:18" ht="97.5">
       <c r="A46" s="80">
         <f t="shared" ref="A46:G49" si="22">A45</f>
         <v>2</v>
@@ -17867,13 +17872,13 @@
         <v>113</v>
       </c>
       <c r="O46" s="26" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="P46" s="14"/>
       <c r="Q46" s="28"/>
       <c r="R46" s="15"/>
     </row>
-    <row r="47" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:18" ht="117">
       <c r="A47" s="80">
         <f t="shared" si="22"/>
         <v>2</v>
@@ -17922,7 +17927,7 @@
         <v>116</v>
       </c>
       <c r="O47" s="26" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="P47" s="14"/>
       <c r="Q47" s="27" t="s">
@@ -17930,7 +17935,7 @@
       </c>
       <c r="R47" s="14"/>
     </row>
-    <row r="48" spans="1:18" ht="234" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:18" ht="234">
       <c r="A48" s="80">
         <f t="shared" si="22"/>
         <v>2</v>
@@ -17978,7 +17983,7 @@
         <v>586</v>
       </c>
       <c r="O48" s="26" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="P48" s="14"/>
       <c r="Q48" s="16" t="s">
@@ -17986,7 +17991,7 @@
       </c>
       <c r="R48" s="14"/>
     </row>
-    <row r="49" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:18" ht="97.5">
       <c r="A49" s="80">
         <f t="shared" si="22"/>
         <v>2</v>
@@ -18040,13 +18045,13 @@
         <v>588</v>
       </c>
       <c r="O49" s="26" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="P49" s="14"/>
       <c r="Q49" s="28"/>
       <c r="R49" s="15"/>
     </row>
-    <row r="50" spans="1:18" ht="234" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:18" ht="234">
       <c r="A50" s="80">
         <f t="shared" ref="A50:D51" si="24">A49</f>
         <v>2</v>
@@ -18091,7 +18096,7 @@
         <v>123</v>
       </c>
       <c r="O50" s="26" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="P50" s="14"/>
       <c r="Q50" s="16" t="s">
@@ -18099,7 +18104,7 @@
       </c>
       <c r="R50" s="14"/>
     </row>
-    <row r="51" spans="1:18" ht="273" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:18" ht="273">
       <c r="A51" s="80">
         <f t="shared" si="24"/>
         <v>2</v>
@@ -18132,7 +18137,7 @@
         <v>592</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="K51" s="26" t="str">
         <f t="shared" si="2"/>
@@ -18144,13 +18149,13 @@
         <v>593</v>
       </c>
       <c r="O51" s="26" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="P51" s="14"/>
       <c r="Q51" s="28"/>
       <c r="R51" s="15"/>
     </row>
-    <row r="52" spans="1:18" ht="273" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:18" ht="273">
       <c r="A52" s="80">
         <f t="shared" ref="A52:G52" si="25">A51</f>
         <v>2</v>
@@ -18210,7 +18215,7 @@
         <v>594</v>
       </c>
       <c r="O52" s="26" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="P52" s="14"/>
       <c r="Q52" s="16" t="s">
@@ -18218,7 +18223,7 @@
       </c>
       <c r="R52" s="14"/>
     </row>
-    <row r="53" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:18" ht="175.5">
       <c r="A53" s="80">
         <f t="shared" ref="A53:D54" si="26">A52</f>
         <v>2</v>
@@ -18263,7 +18268,7 @@
         <v>130</v>
       </c>
       <c r="O53" s="26" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="16" t="s">
@@ -18271,7 +18276,7 @@
       </c>
       <c r="R53" s="14"/>
     </row>
-    <row r="54" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:18" ht="156">
       <c r="A54" s="80">
         <f t="shared" si="26"/>
         <v>2</v>
@@ -18316,7 +18321,7 @@
         <v>601</v>
       </c>
       <c r="O54" s="26" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="P54" s="14"/>
       <c r="Q54" s="16" t="s">
@@ -18324,7 +18329,7 @@
       </c>
       <c r="R54" s="14"/>
     </row>
-    <row r="55" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:18" ht="136.5">
       <c r="A55" s="41">
         <v>3</v>
       </c>
@@ -18364,7 +18369,7 @@
         <v>141</v>
       </c>
       <c r="O55" s="26" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P55" s="14"/>
       <c r="Q55" s="16" t="s">
@@ -18372,7 +18377,7 @@
       </c>
       <c r="R55" s="14"/>
     </row>
-    <row r="56" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:18" ht="117">
       <c r="A56" s="79">
         <f t="shared" ref="A56:A66" si="27">A55</f>
         <v>3</v>
@@ -18423,13 +18428,13 @@
         <v>143</v>
       </c>
       <c r="O56" s="26" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="P56" s="14"/>
       <c r="Q56" s="28"/>
       <c r="R56" s="15"/>
     </row>
-    <row r="57" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:18" ht="136.5">
       <c r="A57" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18478,7 +18483,7 @@
         <v>146</v>
       </c>
       <c r="O57" s="26" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="P57" s="14"/>
       <c r="Q57" s="16" t="s">
@@ -18486,7 +18491,7 @@
       </c>
       <c r="R57" s="14"/>
     </row>
-    <row r="58" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:18" ht="117">
       <c r="A58" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18537,13 +18542,13 @@
         <v>148</v>
       </c>
       <c r="O58" s="26" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="P58" s="14"/>
       <c r="Q58" s="28"/>
       <c r="R58" s="15"/>
     </row>
-    <row r="59" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:18" ht="117">
       <c r="A59" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18592,7 +18597,7 @@
         <v>151</v>
       </c>
       <c r="O59" s="26" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="P59" s="14"/>
       <c r="Q59" s="16" t="s">
@@ -18600,7 +18605,7 @@
       </c>
       <c r="R59" s="14"/>
     </row>
-    <row r="60" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:18" ht="117">
       <c r="A60" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18651,13 +18656,13 @@
         <v>153</v>
       </c>
       <c r="O60" s="26" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="P60" s="14"/>
       <c r="Q60" s="28"/>
       <c r="R60" s="15"/>
     </row>
-    <row r="61" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:18" ht="156">
       <c r="A61" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18706,7 +18711,7 @@
         <v>156</v>
       </c>
       <c r="O61" s="26" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="P61" s="14"/>
       <c r="Q61" s="27" t="s">
@@ -18714,7 +18719,7 @@
       </c>
       <c r="R61" s="14"/>
     </row>
-    <row r="62" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:18" ht="117">
       <c r="A62" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18762,7 +18767,7 @@
         <v>605</v>
       </c>
       <c r="O62" s="26" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="P62" s="14"/>
       <c r="Q62" s="16" t="s">
@@ -18770,7 +18775,7 @@
       </c>
       <c r="R62" s="14"/>
     </row>
-    <row r="63" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:18" ht="117">
       <c r="A63" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18821,13 +18826,13 @@
         <v>607</v>
       </c>
       <c r="O63" s="26" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="P63" s="14"/>
       <c r="Q63" s="28"/>
       <c r="R63" s="15"/>
     </row>
-    <row r="64" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:18" ht="136.5">
       <c r="A64" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18876,7 +18881,7 @@
         <v>610</v>
       </c>
       <c r="O64" s="26" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="P64" s="14"/>
       <c r="Q64" s="16" t="s">
@@ -18884,7 +18889,7 @@
       </c>
       <c r="R64" s="14"/>
     </row>
-    <row r="65" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:18" ht="117">
       <c r="A65" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18935,13 +18940,13 @@
         <v>612</v>
       </c>
       <c r="O65" s="26" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="P65" s="14"/>
       <c r="Q65" s="28"/>
       <c r="R65" s="15"/>
     </row>
-    <row r="66" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:18" ht="156">
       <c r="A66" s="79">
         <f t="shared" si="27"/>
         <v>3</v>
@@ -18990,7 +18995,7 @@
         <v>615</v>
       </c>
       <c r="O66" s="26" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="P66" s="14"/>
       <c r="Q66" s="27" t="s">
@@ -18998,7 +19003,7 @@
       </c>
       <c r="R66" s="14"/>
     </row>
-    <row r="67" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:18" ht="117">
       <c r="A67" s="79">
         <f t="shared" ref="A67:D67" si="37">A66</f>
         <v>3</v>
@@ -19043,7 +19048,7 @@
         <v>163</v>
       </c>
       <c r="O67" s="26" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="P67" s="14"/>
       <c r="Q67" s="16" t="s">
@@ -19051,7 +19056,7 @@
       </c>
       <c r="R67" s="14"/>
     </row>
-    <row r="68" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:18" ht="136.5">
       <c r="A68" s="79">
         <f t="shared" ref="A68:G72" si="38">A67</f>
         <v>3</v>
@@ -19102,13 +19107,13 @@
         <v>165</v>
       </c>
       <c r="O68" s="26" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="28"/>
       <c r="R68" s="15"/>
     </row>
-    <row r="69" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:18" ht="117">
       <c r="A69" s="79">
         <f t="shared" si="38"/>
         <v>3</v>
@@ -19157,7 +19162,7 @@
         <v>168</v>
       </c>
       <c r="O69" s="26" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="P69" s="14"/>
       <c r="Q69" s="16" t="s">
@@ -19165,7 +19170,7 @@
       </c>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:18" ht="136.5">
       <c r="A70" s="79">
         <f t="shared" si="38"/>
         <v>3</v>
@@ -19216,13 +19221,13 @@
         <v>170</v>
       </c>
       <c r="O70" s="26" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="28"/>
       <c r="R70" s="15"/>
     </row>
-    <row r="71" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:18" ht="117">
       <c r="A71" s="79">
         <f t="shared" si="38"/>
         <v>3</v>
@@ -19270,7 +19275,7 @@
         <v>619</v>
       </c>
       <c r="O71" s="26" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="P71" s="14"/>
       <c r="Q71" s="16" t="s">
@@ -19278,7 +19283,7 @@
       </c>
       <c r="R71" s="14"/>
     </row>
-    <row r="72" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:18" ht="117">
       <c r="A72" s="79">
         <f t="shared" si="38"/>
         <v>3</v>
@@ -19327,7 +19332,7 @@
         <v>623</v>
       </c>
       <c r="O72" s="26" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="P72" s="14"/>
       <c r="Q72" s="27" t="s">
@@ -19335,7 +19340,7 @@
       </c>
       <c r="R72" s="14"/>
     </row>
-    <row r="73" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:18" ht="117">
       <c r="A73" s="79">
         <f t="shared" ref="A73:D73" si="40">A72</f>
         <v>3</v>
@@ -19380,7 +19385,7 @@
         <v>176</v>
       </c>
       <c r="O73" s="26" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="P73" s="14"/>
       <c r="Q73" s="16" t="s">
@@ -19388,7 +19393,7 @@
       </c>
       <c r="R73" s="14"/>
     </row>
-    <row r="74" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:18" ht="136.5">
       <c r="A74" s="79">
         <f t="shared" ref="A74:G75" si="41">A73</f>
         <v>3</v>
@@ -19439,13 +19444,13 @@
         <v>178</v>
       </c>
       <c r="O74" s="26" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="P74" s="14"/>
       <c r="Q74" s="28"/>
       <c r="R74" s="15"/>
     </row>
-    <row r="75" spans="1:18" ht="234" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:18" ht="234">
       <c r="A75" s="79">
         <f t="shared" si="41"/>
         <v>3</v>
@@ -19491,10 +19496,10 @@
       <c r="L75" s="14"/>
       <c r="M75" s="14"/>
       <c r="N75" s="26" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="O75" s="26" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="P75" s="14"/>
       <c r="Q75" s="16" t="s">
@@ -19502,7 +19507,7 @@
       </c>
       <c r="R75" s="14"/>
     </row>
-    <row r="76" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:18" ht="117">
       <c r="A76" s="79">
         <f t="shared" ref="A76:D76" si="43">A75</f>
         <v>3</v>
@@ -19547,7 +19552,7 @@
         <v>187</v>
       </c>
       <c r="O76" s="26" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="P76" s="14"/>
       <c r="Q76" s="16" t="s">
@@ -19555,7 +19560,7 @@
       </c>
       <c r="R76" s="14"/>
     </row>
-    <row r="77" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:18" ht="195">
       <c r="A77" s="79">
         <f t="shared" ref="A77:A86" si="44">A76</f>
         <v>3</v>
@@ -19610,13 +19615,13 @@
         <v>189</v>
       </c>
       <c r="O77" s="26" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="P77" s="14"/>
       <c r="Q77" s="28"/>
       <c r="R77" s="15"/>
     </row>
-    <row r="78" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:18" ht="117">
       <c r="A78" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19665,7 +19670,7 @@
         <v>192</v>
       </c>
       <c r="O78" s="26" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="P78" s="14"/>
       <c r="Q78" s="27" t="s">
@@ -19673,7 +19678,7 @@
       </c>
       <c r="R78" s="14"/>
     </row>
-    <row r="79" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:18" ht="156">
       <c r="A79" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19722,7 +19727,7 @@
         <v>196</v>
       </c>
       <c r="O79" s="26" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="P79" s="14"/>
       <c r="Q79" s="16" t="s">
@@ -19730,7 +19735,7 @@
       </c>
       <c r="R79" s="14"/>
     </row>
-    <row r="80" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:18" ht="136.5">
       <c r="A80" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19778,7 +19783,7 @@
         <v>627</v>
       </c>
       <c r="O80" s="26" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="P80" s="14"/>
       <c r="Q80" s="27" t="s">
@@ -19786,7 +19791,7 @@
       </c>
       <c r="R80" s="14"/>
     </row>
-    <row r="81" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:18" ht="117">
       <c r="A81" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19835,13 +19840,13 @@
         <v>631</v>
       </c>
       <c r="O81" s="26" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="P81" s="14"/>
       <c r="Q81" s="28"/>
       <c r="R81" s="15"/>
     </row>
-    <row r="82" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:18" ht="136.5">
       <c r="A82" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19894,13 +19899,13 @@
         <v>632</v>
       </c>
       <c r="O82" s="26" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="P82" s="14"/>
       <c r="Q82" s="28"/>
       <c r="R82" s="15"/>
     </row>
-    <row r="83" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:18" ht="117">
       <c r="A83" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -19953,7 +19958,7 @@
         <v>633</v>
       </c>
       <c r="O83" s="26" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="P83" s="14"/>
       <c r="Q83" s="16" t="s">
@@ -19961,7 +19966,7 @@
       </c>
       <c r="R83" s="14"/>
     </row>
-    <row r="84" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:18" ht="117">
       <c r="A84" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -20010,7 +20015,7 @@
         <v>637</v>
       </c>
       <c r="O84" s="26" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="27" t="s">
@@ -20018,7 +20023,7 @@
       </c>
       <c r="R84" s="14"/>
     </row>
-    <row r="85" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:18" ht="175.5">
       <c r="A85" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -20067,7 +20072,7 @@
         <v>641</v>
       </c>
       <c r="O85" s="26" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="P85" s="14"/>
       <c r="Q85" s="16" t="s">
@@ -20075,7 +20080,7 @@
       </c>
       <c r="R85" s="14"/>
     </row>
-    <row r="86" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:18" ht="156">
       <c r="A86" s="79">
         <f t="shared" si="44"/>
         <v>3</v>
@@ -20124,7 +20129,7 @@
         <v>645</v>
       </c>
       <c r="O86" s="26" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="P86" s="14"/>
       <c r="Q86" s="16" t="s">
@@ -20132,7 +20137,7 @@
       </c>
       <c r="R86" s="14"/>
     </row>
-    <row r="87" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:18" ht="156">
       <c r="A87" s="79">
         <f t="shared" ref="A87:D87" si="55">A86</f>
         <v>3</v>
@@ -20177,7 +20182,7 @@
         <v>652</v>
       </c>
       <c r="O87" s="26" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="P87" s="14"/>
       <c r="Q87" s="16" t="s">
@@ -20185,7 +20190,7 @@
       </c>
       <c r="R87" s="14"/>
     </row>
-    <row r="88" spans="1:18" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:18" ht="214.5">
       <c r="A88" s="79">
         <f t="shared" ref="A88:G91" si="56">A87</f>
         <v>3</v>
@@ -20238,13 +20243,13 @@
         <v>654</v>
       </c>
       <c r="O88" s="26" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="P88" s="14"/>
       <c r="Q88" s="28"/>
       <c r="R88" s="15"/>
     </row>
-    <row r="89" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:18" ht="156">
       <c r="A89" s="79">
         <f t="shared" si="56"/>
         <v>3</v>
@@ -20293,7 +20298,7 @@
         <v>657</v>
       </c>
       <c r="O89" s="26" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="P89" s="14"/>
       <c r="Q89" s="16" t="s">
@@ -20301,7 +20306,7 @@
       </c>
       <c r="R89" s="14"/>
     </row>
-    <row r="90" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:18" ht="136.5">
       <c r="A90" s="79">
         <f t="shared" si="56"/>
         <v>3</v>
@@ -20350,7 +20355,7 @@
         <v>661</v>
       </c>
       <c r="O90" s="26" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="P90" s="14"/>
       <c r="Q90" s="27" t="s">
@@ -20358,7 +20363,7 @@
       </c>
       <c r="R90" s="14"/>
     </row>
-    <row r="91" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:18" ht="136.5">
       <c r="A91" s="79">
         <f t="shared" si="56"/>
         <v>3</v>
@@ -20409,13 +20414,13 @@
         <v>663</v>
       </c>
       <c r="O91" s="26" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="P91" s="14"/>
       <c r="Q91" s="28"/>
       <c r="R91" s="15"/>
     </row>
-    <row r="92" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:18" ht="156">
       <c r="A92" s="79">
         <f t="shared" ref="A92:B92" si="58">A91</f>
         <v>3</v>
@@ -20458,7 +20463,7 @@
         <v>671</v>
       </c>
       <c r="O92" s="26" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="P92" s="14"/>
       <c r="Q92" s="16" t="s">
@@ -20466,7 +20471,7 @@
       </c>
       <c r="R92" s="14"/>
     </row>
-    <row r="93" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:18" ht="136.5">
       <c r="A93" s="79">
         <f t="shared" ref="A93:G97" si="59">A92</f>
         <v>3</v>
@@ -20515,7 +20520,7 @@
         <v>675</v>
       </c>
       <c r="O93" s="26" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="P93" s="14"/>
       <c r="Q93" s="16" t="s">
@@ -20523,7 +20528,7 @@
       </c>
       <c r="R93" s="14"/>
     </row>
-    <row r="94" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:18" ht="136.5">
       <c r="A94" s="79">
         <f t="shared" si="59"/>
         <v>3</v>
@@ -20572,7 +20577,7 @@
         <v>679</v>
       </c>
       <c r="O94" s="26" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="P94" s="14"/>
       <c r="Q94" s="16" t="s">
@@ -20580,7 +20585,7 @@
       </c>
       <c r="R94" s="14"/>
     </row>
-    <row r="95" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:18" ht="136.5">
       <c r="A95" s="79">
         <f t="shared" si="59"/>
         <v>3</v>
@@ -20629,7 +20634,7 @@
         <v>683</v>
       </c>
       <c r="O95" s="26" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="P95" s="14"/>
       <c r="Q95" s="16" t="s">
@@ -20637,7 +20642,7 @@
       </c>
       <c r="R95" s="14"/>
     </row>
-    <row r="96" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:18" ht="117">
       <c r="A96" s="79">
         <f t="shared" si="59"/>
         <v>3</v>
@@ -20686,13 +20691,13 @@
         <v>687</v>
       </c>
       <c r="O96" s="26" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="P96" s="14"/>
       <c r="Q96" s="28"/>
       <c r="R96" s="15"/>
     </row>
-    <row r="97" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:18" ht="117">
       <c r="A97" s="79">
         <f t="shared" si="59"/>
         <v>3</v>
@@ -20743,7 +20748,7 @@
         <v>688</v>
       </c>
       <c r="O97" s="26" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="P97" s="14"/>
       <c r="Q97" s="27" t="s">
@@ -20751,7 +20756,7 @@
       </c>
       <c r="R97" s="14"/>
     </row>
-    <row r="98" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:18" ht="156">
       <c r="A98" s="42">
         <v>4</v>
       </c>
@@ -20791,15 +20796,15 @@
         <v>207</v>
       </c>
       <c r="O98" s="26" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="16" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="R98" s="14"/>
     </row>
-    <row r="99" spans="1:18" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:18" ht="214.5">
       <c r="A99" s="77">
         <f t="shared" ref="A99:G101" si="62">A98</f>
         <v>4</v>
@@ -20848,7 +20853,7 @@
         <v>210</v>
       </c>
       <c r="O99" s="26" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="P99" s="14"/>
       <c r="Q99" s="16" t="s">
@@ -20856,7 +20861,7 @@
       </c>
       <c r="R99" s="14"/>
     </row>
-    <row r="100" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:18" ht="136.5">
       <c r="A100" s="77">
         <f t="shared" si="62"/>
         <v>4</v>
@@ -20905,7 +20910,7 @@
         <v>214</v>
       </c>
       <c r="O100" s="26" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="P100" s="14"/>
       <c r="Q100" s="16" t="s">
@@ -20913,7 +20918,7 @@
       </c>
       <c r="R100" s="14"/>
     </row>
-    <row r="101" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:18" ht="136.5">
       <c r="A101" s="77">
         <f t="shared" si="62"/>
         <v>4</v>
@@ -20962,15 +20967,15 @@
         <v>218</v>
       </c>
       <c r="O101" s="26" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="P101" s="14"/>
       <c r="Q101" s="16" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="R101" s="14"/>
     </row>
-    <row r="102" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:18" ht="136.5">
       <c r="A102" s="77">
         <f t="shared" ref="A102:D102" si="65">A101</f>
         <v>4</v>
@@ -21015,15 +21020,15 @@
         <v>224</v>
       </c>
       <c r="O102" s="26" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="P102" s="14"/>
       <c r="Q102" s="16" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" spans="1:18" ht="273" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:18" ht="273">
       <c r="A103" s="77">
         <f t="shared" ref="A103:G110" si="66">A102</f>
         <v>4</v>
@@ -21072,7 +21077,7 @@
         <v>227</v>
       </c>
       <c r="O103" s="26" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="P103" s="14"/>
       <c r="Q103" s="16" t="s">
@@ -21080,7 +21085,7 @@
       </c>
       <c r="R103" s="14"/>
     </row>
-    <row r="104" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:18" ht="136.5">
       <c r="A104" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21129,7 +21134,7 @@
         <v>231</v>
       </c>
       <c r="O104" s="26" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="P104" s="14"/>
       <c r="Q104" s="16" t="s">
@@ -21137,7 +21142,7 @@
       </c>
       <c r="R104" s="14"/>
     </row>
-    <row r="105" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:18" ht="156">
       <c r="A105" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21186,7 +21191,7 @@
         <v>235</v>
       </c>
       <c r="O105" s="26" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="P105" s="14"/>
       <c r="Q105" s="16" t="s">
@@ -21194,7 +21199,7 @@
       </c>
       <c r="R105" s="14"/>
     </row>
-    <row r="106" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:18" ht="136.5">
       <c r="A106" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21243,7 +21248,7 @@
         <v>239</v>
       </c>
       <c r="O106" s="26" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="P106" s="14"/>
       <c r="Q106" s="16" t="s">
@@ -21251,7 +21256,7 @@
       </c>
       <c r="R106" s="14"/>
     </row>
-    <row r="107" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:18" ht="136.5">
       <c r="A107" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21300,7 +21305,7 @@
         <v>243</v>
       </c>
       <c r="O107" s="26" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="P107" s="14"/>
       <c r="Q107" s="16" t="s">
@@ -21308,7 +21313,7 @@
       </c>
       <c r="R107" s="14"/>
     </row>
-    <row r="108" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:18" ht="117">
       <c r="A108" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21357,7 +21362,7 @@
         <v>247</v>
       </c>
       <c r="O108" s="26" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="P108" s="14"/>
       <c r="Q108" s="16" t="s">
@@ -21365,7 +21370,7 @@
       </c>
       <c r="R108" s="14"/>
     </row>
-    <row r="109" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:18" ht="136.5">
       <c r="A109" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21414,7 +21419,7 @@
         <v>251</v>
       </c>
       <c r="O109" s="26" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="P109" s="14"/>
       <c r="Q109" s="16" t="s">
@@ -21422,7 +21427,7 @@
       </c>
       <c r="R109" s="14"/>
     </row>
-    <row r="110" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:18" ht="136.5">
       <c r="A110" s="77">
         <f t="shared" si="66"/>
         <v>4</v>
@@ -21473,7 +21478,7 @@
         <v>253</v>
       </c>
       <c r="O110" s="26" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="P110" s="14"/>
       <c r="Q110" s="16" t="s">
@@ -21481,7 +21486,7 @@
       </c>
       <c r="R110" s="14"/>
     </row>
-    <row r="111" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:18" ht="156">
       <c r="A111" s="77">
         <f t="shared" ref="A111:D111" si="68">A110</f>
         <v>4</v>
@@ -21526,7 +21531,7 @@
         <v>260</v>
       </c>
       <c r="O111" s="26" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="P111" s="14"/>
       <c r="Q111" s="16" t="s">
@@ -21534,7 +21539,7 @@
       </c>
       <c r="R111" s="14"/>
     </row>
-    <row r="112" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:18" ht="97.5">
       <c r="A112" s="77">
         <f t="shared" ref="A112:G118" si="69">A111</f>
         <v>4</v>
@@ -21583,7 +21588,7 @@
         <v>264</v>
       </c>
       <c r="O112" s="26" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="16" t="s">
@@ -21591,7 +21596,7 @@
       </c>
       <c r="R112" s="14"/>
     </row>
-    <row r="113" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:18" ht="156">
       <c r="A113" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21643,7 +21648,7 @@
         <v>①重要な機密情報を取り扱うクラウドサービスにユーザ又は管理者がアクセスする場合、常にNo.4-1-3-3で示す2種類以上の認証要素を利用した多要素認証を使用していること。</v>
       </c>
       <c r="O113" s="26" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="P113" s="14"/>
       <c r="Q113" s="16" t="s">
@@ -21651,7 +21656,7 @@
       </c>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" spans="1:18" ht="331.5" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:18" ht="331.5">
       <c r="A114" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21700,13 +21705,13 @@
         <v>269</v>
       </c>
       <c r="O114" s="26" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="P114" s="14"/>
       <c r="Q114" s="28"/>
       <c r="R114" s="15"/>
     </row>
-    <row r="115" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:18" ht="117">
       <c r="A115" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21755,7 +21760,7 @@
         <v>272</v>
       </c>
       <c r="O115" s="26" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="P115" s="14"/>
       <c r="Q115" s="16" t="s">
@@ -21763,7 +21768,7 @@
       </c>
       <c r="R115" s="14"/>
     </row>
-    <row r="116" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:18" ht="136.5">
       <c r="A116" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21811,7 +21816,7 @@
         <v>693</v>
       </c>
       <c r="O116" s="26" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="P116" s="14"/>
       <c r="Q116" s="16" t="s">
@@ -21819,7 +21824,7 @@
       </c>
       <c r="R116" s="14"/>
     </row>
-    <row r="117" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:18" ht="117">
       <c r="A117" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21873,13 +21878,13 @@
         <v>695</v>
       </c>
       <c r="O117" s="26" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="P117" s="14"/>
       <c r="Q117" s="28"/>
       <c r="R117" s="15"/>
     </row>
-    <row r="118" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:18" ht="136.5">
       <c r="A118" s="77">
         <f t="shared" si="69"/>
         <v>4</v>
@@ -21933,13 +21938,13 @@
         <v>696</v>
       </c>
       <c r="O118" s="26" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="P118" s="14"/>
       <c r="Q118" s="28"/>
       <c r="R118" s="15"/>
     </row>
-    <row r="119" spans="1:18" ht="273" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:18" ht="273">
       <c r="A119" s="77">
         <f t="shared" ref="A119:D119" si="74">A118</f>
         <v>4</v>
@@ -21984,7 +21989,7 @@
         <v>279</v>
       </c>
       <c r="O119" s="26" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="16" t="s">
@@ -21992,7 +21997,7 @@
       </c>
       <c r="R119" s="14"/>
     </row>
-    <row r="120" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:18" ht="156">
       <c r="A120" s="77">
         <f t="shared" ref="A120:G120" si="75">A119</f>
         <v>4</v>
@@ -22041,7 +22046,7 @@
         <v>283</v>
       </c>
       <c r="O120" s="26" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="P120" s="14"/>
       <c r="Q120" s="16" t="s">
@@ -22049,7 +22054,7 @@
       </c>
       <c r="R120" s="14"/>
     </row>
-    <row r="121" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:18" ht="156">
       <c r="A121" s="77">
         <f t="shared" ref="A121:D121" si="76">A120</f>
         <v>4</v>
@@ -22094,7 +22099,7 @@
         <v>290</v>
       </c>
       <c r="O121" s="26" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="P121" s="14"/>
       <c r="Q121" s="16" t="s">
@@ -22102,7 +22107,7 @@
       </c>
       <c r="R121" s="14"/>
     </row>
-    <row r="122" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:18" ht="156">
       <c r="A122" s="77">
         <f t="shared" ref="A122:G126" si="77">A121</f>
         <v>4</v>
@@ -22151,7 +22156,7 @@
         <v>294</v>
       </c>
       <c r="O122" s="26" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="P122" s="14"/>
       <c r="Q122" s="16" t="s">
@@ -22159,7 +22164,7 @@
       </c>
       <c r="R122" s="14"/>
     </row>
-    <row r="123" spans="1:18" ht="331.5" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:18" ht="331.5">
       <c r="A123" s="77">
         <f t="shared" si="77"/>
         <v>4</v>
@@ -22208,7 +22213,7 @@
         <v>298</v>
       </c>
       <c r="O123" s="26" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="P123" s="14"/>
       <c r="Q123" s="16" t="s">
@@ -22216,7 +22221,7 @@
       </c>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:18" ht="136.5">
       <c r="A124" s="77">
         <f t="shared" si="77"/>
         <v>4</v>
@@ -22269,13 +22274,13 @@
         <v>300</v>
       </c>
       <c r="O124" s="26" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="P124" s="14"/>
       <c r="Q124" s="28"/>
       <c r="R124" s="15"/>
     </row>
-    <row r="125" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:18" ht="156">
       <c r="A125" s="77">
         <f t="shared" si="77"/>
         <v>4</v>
@@ -22324,7 +22329,7 @@
         <v>303</v>
       </c>
       <c r="O125" s="26" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="P125" s="14"/>
       <c r="Q125" s="16" t="s">
@@ -22332,7 +22337,7 @@
       </c>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:18" ht="156">
       <c r="A126" s="77">
         <f t="shared" si="77"/>
         <v>4</v>
@@ -22381,7 +22386,7 @@
         <v>307</v>
       </c>
       <c r="O126" s="26" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="P126" s="14"/>
       <c r="Q126" s="16" t="s">
@@ -22389,7 +22394,7 @@
       </c>
       <c r="R126" s="14"/>
     </row>
-    <row r="127" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:18" ht="156">
       <c r="A127" s="77">
         <f t="shared" ref="A127:D127" si="79">A126</f>
         <v>4</v>
@@ -22434,7 +22439,7 @@
         <v>314</v>
       </c>
       <c r="O127" s="26" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="P127" s="14"/>
       <c r="Q127" s="16" t="s">
@@ -22442,7 +22447,7 @@
       </c>
       <c r="R127" s="14"/>
     </row>
-    <row r="128" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:18" ht="156">
       <c r="A128" s="77">
         <f t="shared" ref="A128:G130" si="80">A127</f>
         <v>4</v>
@@ -22491,13 +22496,13 @@
         <v>318</v>
       </c>
       <c r="O128" s="26" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="P128" s="14"/>
       <c r="Q128" s="28"/>
       <c r="R128" s="15"/>
     </row>
-    <row r="129" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:18" ht="136.5">
       <c r="A129" s="77">
         <f t="shared" si="80"/>
         <v>4</v>
@@ -22548,7 +22553,7 @@
         <v>319</v>
       </c>
       <c r="O129" s="26" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="P129" s="14"/>
       <c r="Q129" s="16" t="s">
@@ -22556,7 +22561,7 @@
       </c>
       <c r="R129" s="14"/>
     </row>
-    <row r="130" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:18" ht="156">
       <c r="A130" s="77">
         <f t="shared" si="80"/>
         <v>4</v>
@@ -22605,7 +22610,7 @@
         <v>323</v>
       </c>
       <c r="O130" s="26" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="P130" s="14"/>
       <c r="Q130" s="16" t="s">
@@ -22613,7 +22618,7 @@
       </c>
       <c r="R130" s="14"/>
     </row>
-    <row r="131" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:18" ht="156">
       <c r="A131" s="77">
         <f t="shared" ref="A131:D131" si="82">A130</f>
         <v>4</v>
@@ -22658,7 +22663,7 @@
         <v>330</v>
       </c>
       <c r="O131" s="26" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="P131" s="14"/>
       <c r="Q131" s="16" t="s">
@@ -22666,7 +22671,7 @@
       </c>
       <c r="R131" s="14"/>
     </row>
-    <row r="132" spans="1:18" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:18" ht="292.5">
       <c r="A132" s="77">
         <f t="shared" ref="A132:G137" si="84">A131</f>
         <v>4</v>
@@ -22721,13 +22726,13 @@
         <v>332</v>
       </c>
       <c r="O132" s="26" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="P132" s="14"/>
       <c r="Q132" s="28"/>
       <c r="R132" s="15"/>
     </row>
-    <row r="133" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:18" ht="136.5">
       <c r="A133" s="77">
         <f t="shared" si="84"/>
         <v>4</v>
@@ -22775,7 +22780,7 @@
         <v>699</v>
       </c>
       <c r="O133" s="26" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="P133" s="14"/>
       <c r="Q133" s="27" t="s">
@@ -22783,7 +22788,7 @@
       </c>
       <c r="R133" s="14"/>
     </row>
-    <row r="134" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:18" ht="136.5">
       <c r="A134" s="77">
         <f t="shared" si="84"/>
         <v>4</v>
@@ -22832,7 +22837,7 @@
         <v>703</v>
       </c>
       <c r="O134" s="26" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="P134" s="14"/>
       <c r="Q134" s="16" t="s">
@@ -22840,7 +22845,7 @@
       </c>
       <c r="R134" s="14"/>
     </row>
-    <row r="135" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:18" ht="136.5">
       <c r="A135" s="77">
         <f t="shared" si="84"/>
         <v>4</v>
@@ -22889,7 +22894,7 @@
         <v>707</v>
       </c>
       <c r="O135" s="26" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="P135" s="14"/>
       <c r="Q135" s="16" t="s">
@@ -22897,7 +22902,7 @@
       </c>
       <c r="R135" s="14"/>
     </row>
-    <row r="136" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:18" ht="156">
       <c r="A136" s="77">
         <f t="shared" si="84"/>
         <v>4</v>
@@ -22946,7 +22951,7 @@
         <v>711</v>
       </c>
       <c r="O136" s="26" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="P136" s="14"/>
       <c r="Q136" s="16" t="s">
@@ -22954,7 +22959,7 @@
       </c>
       <c r="R136" s="14"/>
     </row>
-    <row r="137" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:18" ht="136.5">
       <c r="A137" s="77">
         <f t="shared" si="84"/>
         <v>4</v>
@@ -23003,7 +23008,7 @@
         <v>715</v>
       </c>
       <c r="O137" s="26" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="P137" s="14"/>
       <c r="Q137" s="16" t="s">
@@ -23011,7 +23016,7 @@
       </c>
       <c r="R137" s="14"/>
     </row>
-    <row r="138" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:18" ht="117">
       <c r="A138" s="77">
         <f t="shared" ref="A138:D138" si="86">A137</f>
         <v>4</v>
@@ -23056,7 +23061,7 @@
         <v>722</v>
       </c>
       <c r="O138" s="26" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="P138" s="14"/>
       <c r="Q138" s="16" t="s">
@@ -23064,7 +23069,7 @@
       </c>
       <c r="R138" s="14"/>
     </row>
-    <row r="139" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:18" ht="175.5">
       <c r="A139" s="77">
         <f t="shared" ref="A139:G143" si="87">A138</f>
         <v>4</v>
@@ -23113,7 +23118,7 @@
         <v>726</v>
       </c>
       <c r="O139" s="26" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="P139" s="14"/>
       <c r="Q139" s="27" t="s">
@@ -23121,7 +23126,7 @@
       </c>
       <c r="R139" s="14"/>
     </row>
-    <row r="140" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:18" ht="136.5">
       <c r="A140" s="77">
         <f t="shared" si="87"/>
         <v>4</v>
@@ -23170,7 +23175,7 @@
         <v>730</v>
       </c>
       <c r="O140" s="26" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="P140" s="14"/>
       <c r="Q140" s="16" t="s">
@@ -23178,7 +23183,7 @@
       </c>
       <c r="R140" s="14"/>
     </row>
-    <row r="141" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:18" ht="136.5">
       <c r="A141" s="77">
         <f t="shared" si="87"/>
         <v>4</v>
@@ -23229,7 +23234,7 @@
         <v>732</v>
       </c>
       <c r="O141" s="26" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="P141" s="14"/>
       <c r="Q141" s="16" t="s">
@@ -23237,7 +23242,7 @@
       </c>
       <c r="R141" s="14"/>
     </row>
-    <row r="142" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:18" ht="136.5">
       <c r="A142" s="77">
         <f t="shared" si="87"/>
         <v>4</v>
@@ -23286,7 +23291,7 @@
         <v>736</v>
       </c>
       <c r="O142" s="26" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="P142" s="14"/>
       <c r="Q142" s="16" t="s">
@@ -23294,7 +23299,7 @@
       </c>
       <c r="R142" s="14"/>
     </row>
-    <row r="143" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:18" ht="97.5">
       <c r="A143" s="77">
         <f t="shared" si="87"/>
         <v>4</v>
@@ -23345,7 +23350,7 @@
         <v>738</v>
       </c>
       <c r="O143" s="26" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="P143" s="14"/>
       <c r="Q143" s="16" t="s">
@@ -23353,7 +23358,7 @@
       </c>
       <c r="R143" s="14"/>
     </row>
-    <row r="144" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:18" ht="136.5">
       <c r="A144" s="77">
         <f t="shared" ref="A144:D144" si="89">A143</f>
         <v>4</v>
@@ -23398,7 +23403,7 @@
         <v>745</v>
       </c>
       <c r="O144" s="26" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="P144" s="14"/>
       <c r="Q144" s="16" t="s">
@@ -23406,7 +23411,7 @@
       </c>
       <c r="R144" s="14"/>
     </row>
-    <row r="145" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:18" ht="156">
       <c r="A145" s="77">
         <f t="shared" ref="A145:G147" si="90">A144</f>
         <v>4</v>
@@ -23455,7 +23460,7 @@
         <v>749</v>
       </c>
       <c r="O145" s="26" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="P145" s="14"/>
       <c r="Q145" s="16" t="s">
@@ -23463,7 +23468,7 @@
       </c>
       <c r="R145" s="14"/>
     </row>
-    <row r="146" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:18" ht="195">
       <c r="A146" s="77">
         <f t="shared" si="90"/>
         <v>4</v>
@@ -23512,15 +23517,15 @@
         <v>753</v>
       </c>
       <c r="O146" s="26" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="P146" s="14"/>
       <c r="Q146" s="27" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="R146" s="14"/>
     </row>
-    <row r="147" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:18" ht="195">
       <c r="A147" s="77">
         <f t="shared" si="90"/>
         <v>4</v>
@@ -23571,15 +23576,15 @@
         <v>754</v>
       </c>
       <c r="O147" s="26" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="P147" s="14"/>
       <c r="Q147" s="27" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="R147" s="14"/>
     </row>
-    <row r="148" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:18" ht="156">
       <c r="A148" s="77">
         <f t="shared" ref="A148:B148" si="92">A147</f>
         <v>4</v>
@@ -23601,7 +23606,7 @@
         <v>758</v>
       </c>
       <c r="G148" s="26" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="H148" s="26" t="s">
         <v>519</v>
@@ -23622,7 +23627,7 @@
         <v>761</v>
       </c>
       <c r="O148" s="26" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="P148" s="14"/>
       <c r="Q148" s="16" t="s">
@@ -23630,7 +23635,7 @@
       </c>
       <c r="R148" s="14"/>
     </row>
-    <row r="149" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:18" ht="175.5">
       <c r="A149" s="77">
         <f t="shared" ref="A149:G154" si="93">A148</f>
         <v>4</v>
@@ -23679,7 +23684,7 @@
         <v>765</v>
       </c>
       <c r="O149" s="26" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="P149" s="14"/>
       <c r="Q149" s="16" t="s">
@@ -23687,7 +23692,7 @@
       </c>
       <c r="R149" s="14"/>
     </row>
-    <row r="150" spans="1:18" ht="234" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:18" ht="234">
       <c r="A150" s="77">
         <f t="shared" si="93"/>
         <v>4</v>
@@ -23736,7 +23741,7 @@
         <v>769</v>
       </c>
       <c r="O150" s="26" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="P150" s="14"/>
       <c r="Q150" s="16" t="s">
@@ -23744,7 +23749,7 @@
       </c>
       <c r="R150" s="14"/>
     </row>
-    <row r="151" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:18" ht="136.5">
       <c r="A151" s="77">
         <f t="shared" si="93"/>
         <v>4</v>
@@ -23798,7 +23803,7 @@
         <v>771</v>
       </c>
       <c r="O151" s="26" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="P151" s="14"/>
       <c r="Q151" s="16" t="s">
@@ -23806,7 +23811,7 @@
       </c>
       <c r="R151" s="14"/>
     </row>
-    <row r="152" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:18" ht="136.5">
       <c r="A152" s="77">
         <f t="shared" si="93"/>
         <v>4</v>
@@ -23855,7 +23860,7 @@
         <v>775</v>
       </c>
       <c r="O152" s="26" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="P152" s="14"/>
       <c r="Q152" s="16" t="s">
@@ -23863,7 +23868,7 @@
       </c>
       <c r="R152" s="14"/>
     </row>
-    <row r="153" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:18" ht="117">
       <c r="A153" s="77">
         <f t="shared" si="93"/>
         <v>4</v>
@@ -23914,13 +23919,13 @@
         <v>777</v>
       </c>
       <c r="O153" s="26" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="P153" s="14"/>
       <c r="Q153" s="28"/>
       <c r="R153" s="15"/>
     </row>
-    <row r="154" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:18" ht="136.5">
       <c r="A154" s="77">
         <f t="shared" si="93"/>
         <v>4</v>
@@ -23969,7 +23974,7 @@
         <v>780</v>
       </c>
       <c r="O154" s="26" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="P154" s="14"/>
       <c r="Q154" s="27" t="s">
@@ -23977,7 +23982,7 @@
       </c>
       <c r="R154" s="14"/>
     </row>
-    <row r="155" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:18" ht="195">
       <c r="A155" s="77">
         <f t="shared" ref="A155:D155" si="95">A154</f>
         <v>4</v>
@@ -24022,7 +24027,7 @@
         <v>338</v>
       </c>
       <c r="O155" s="26" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="P155" s="14"/>
       <c r="Q155" s="16" t="s">
@@ -24030,7 +24035,7 @@
       </c>
       <c r="R155" s="14"/>
     </row>
-    <row r="156" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:18" ht="136.5">
       <c r="A156" s="77">
         <f t="shared" ref="A156:G159" si="96">A155</f>
         <v>4</v>
@@ -24081,7 +24086,7 @@
         <v>340</v>
       </c>
       <c r="O156" s="26" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="P156" s="14"/>
       <c r="Q156" s="16" t="s">
@@ -24089,7 +24094,7 @@
       </c>
       <c r="R156" s="14"/>
     </row>
-    <row r="157" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:18" ht="156">
       <c r="A157" s="77">
         <f t="shared" si="96"/>
         <v>4</v>
@@ -24138,7 +24143,7 @@
         <v>344</v>
       </c>
       <c r="O157" s="26" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="P157" s="14"/>
       <c r="Q157" s="16" t="s">
@@ -24146,7 +24151,7 @@
       </c>
       <c r="R157" s="14"/>
     </row>
-    <row r="158" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:18" ht="97.5">
       <c r="A158" s="77">
         <f t="shared" si="96"/>
         <v>4</v>
@@ -24197,13 +24202,13 @@
         <v>346</v>
       </c>
       <c r="O158" s="26" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="P158" s="14"/>
       <c r="Q158" s="28"/>
       <c r="R158" s="15"/>
     </row>
-    <row r="159" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:18" ht="136.5">
       <c r="A159" s="77">
         <f t="shared" si="96"/>
         <v>4</v>
@@ -24252,7 +24257,7 @@
         <v>349</v>
       </c>
       <c r="O159" s="26" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="P159" s="14"/>
       <c r="Q159" s="16" t="s">
@@ -24260,7 +24265,7 @@
       </c>
       <c r="R159" s="14"/>
     </row>
-    <row r="160" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:18" ht="156">
       <c r="A160" s="77">
         <f t="shared" ref="A160:B160" si="98">A159</f>
         <v>4</v>
@@ -24303,7 +24308,7 @@
         <v>789</v>
       </c>
       <c r="O160" s="26" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="P160" s="14"/>
       <c r="Q160" s="16" t="s">
@@ -24311,7 +24316,7 @@
       </c>
       <c r="R160" s="14"/>
     </row>
-    <row r="161" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:18" ht="156">
       <c r="A161" s="77">
         <f t="shared" ref="A161:G165" si="99">A160</f>
         <v>4</v>
@@ -24362,7 +24367,7 @@
         <v>791</v>
       </c>
       <c r="O161" s="26" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="P161" s="14"/>
       <c r="Q161" s="16" t="s">
@@ -24370,7 +24375,7 @@
       </c>
       <c r="R161" s="14"/>
     </row>
-    <row r="162" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:18" ht="136.5">
       <c r="A162" s="77">
         <f t="shared" si="99"/>
         <v>4</v>
@@ -24421,13 +24426,13 @@
         <v>793</v>
       </c>
       <c r="O162" s="26" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="P162" s="14"/>
       <c r="Q162" s="28"/>
       <c r="R162" s="15"/>
     </row>
-    <row r="163" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:18" ht="136.5">
       <c r="A163" s="77">
         <f t="shared" si="99"/>
         <v>4</v>
@@ -24476,7 +24481,7 @@
         <v>796</v>
       </c>
       <c r="O163" s="26" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="P163" s="14"/>
       <c r="Q163" s="16" t="s">
@@ -24484,7 +24489,7 @@
       </c>
       <c r="R163" s="14"/>
     </row>
-    <row r="164" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:18" ht="136.5">
       <c r="A164" s="77">
         <f t="shared" si="99"/>
         <v>4</v>
@@ -24535,7 +24540,7 @@
         <v>791</v>
       </c>
       <c r="O164" s="26" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="P164" s="14"/>
       <c r="Q164" s="16" t="s">
@@ -24543,7 +24548,7 @@
       </c>
       <c r="R164" s="14"/>
     </row>
-    <row r="165" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:18" ht="117">
       <c r="A165" s="77">
         <f t="shared" si="99"/>
         <v>4</v>
@@ -24594,13 +24599,13 @@
         <v>799</v>
       </c>
       <c r="O165" s="26" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="P165" s="14"/>
       <c r="Q165" s="28"/>
       <c r="R165" s="15"/>
     </row>
-    <row r="166" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:18" ht="156">
       <c r="A166" s="77">
         <f t="shared" ref="A166:D166" si="106">A165</f>
         <v>4</v>
@@ -24645,13 +24650,13 @@
         <v>805</v>
       </c>
       <c r="O166" s="26" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="P166" s="14"/>
       <c r="Q166" s="28"/>
       <c r="R166" s="15"/>
     </row>
-    <row r="167" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:18" ht="117">
       <c r="A167" s="77">
         <f t="shared" ref="A167:G169" si="107">A166</f>
         <v>4</v>
@@ -24702,7 +24707,7 @@
         <v>806</v>
       </c>
       <c r="O167" s="26" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="P167" s="14"/>
       <c r="Q167" s="27" t="s">
@@ -24710,7 +24715,7 @@
       </c>
       <c r="R167" s="14"/>
     </row>
-    <row r="168" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:18" ht="156">
       <c r="A168" s="77">
         <f t="shared" si="107"/>
         <v>4</v>
@@ -24761,7 +24766,7 @@
         <v>808</v>
       </c>
       <c r="O168" s="26" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="P168" s="14"/>
       <c r="Q168" s="27" t="s">
@@ -24769,7 +24774,7 @@
       </c>
       <c r="R168" s="14"/>
     </row>
-    <row r="169" spans="1:18" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:18" ht="97.5">
       <c r="A169" s="77">
         <f t="shared" si="107"/>
         <v>4</v>
@@ -24820,13 +24825,13 @@
         <v>810</v>
       </c>
       <c r="O169" s="26" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="P169" s="14"/>
       <c r="Q169" s="28"/>
       <c r="R169" s="15"/>
     </row>
-    <row r="170" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:18" ht="136.5">
       <c r="A170" s="77">
         <f t="shared" ref="A170:D170" si="111">A169</f>
         <v>4</v>
@@ -24871,7 +24876,7 @@
         <v>816</v>
       </c>
       <c r="O170" s="26" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="P170" s="14"/>
       <c r="Q170" s="16" t="s">
@@ -24879,7 +24884,7 @@
       </c>
       <c r="R170" s="14"/>
     </row>
-    <row r="171" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:18" ht="175.5">
       <c r="A171" s="77">
         <f t="shared" ref="A171:G172" si="112">A170</f>
         <v>4</v>
@@ -24932,13 +24937,13 @@
         <v>818</v>
       </c>
       <c r="O171" s="26" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="P171" s="14"/>
       <c r="Q171" s="28"/>
       <c r="R171" s="15"/>
     </row>
-    <row r="172" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:18" ht="156">
       <c r="A172" s="77">
         <f t="shared" si="112"/>
         <v>4</v>
@@ -24991,7 +24996,7 @@
         <v>819</v>
       </c>
       <c r="O172" s="26" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="P172" s="14"/>
       <c r="Q172" s="16" t="s">
@@ -24999,7 +25004,7 @@
       </c>
       <c r="R172" s="14"/>
     </row>
-    <row r="173" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:18" ht="156">
       <c r="A173" s="77">
         <f t="shared" ref="A173:D173" si="116">A172</f>
         <v>4</v>
@@ -25044,7 +25049,7 @@
         <v>356</v>
       </c>
       <c r="O173" s="26" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="P173" s="14"/>
       <c r="Q173" s="16" t="s">
@@ -25052,7 +25057,7 @@
       </c>
       <c r="R173" s="14"/>
     </row>
-    <row r="174" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:18" ht="117">
       <c r="A174" s="77">
         <f t="shared" ref="A174:G176" si="117">A173</f>
         <v>4</v>
@@ -25103,13 +25108,13 @@
         <v>358</v>
       </c>
       <c r="O174" s="26" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="P174" s="14"/>
       <c r="Q174" s="28"/>
       <c r="R174" s="15"/>
     </row>
-    <row r="175" spans="1:18" ht="234" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:18" ht="234">
       <c r="A175" s="77">
         <f t="shared" si="117"/>
         <v>4</v>
@@ -25155,10 +25160,10 @@
       <c r="L175" s="14"/>
       <c r="M175" s="14"/>
       <c r="N175" s="26" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="O175" s="26" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="P175" s="14"/>
       <c r="Q175" s="16" t="s">
@@ -25166,7 +25171,7 @@
       </c>
       <c r="R175" s="14"/>
     </row>
-    <row r="176" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:18" ht="117">
       <c r="A176" s="77">
         <f t="shared" si="117"/>
         <v>4</v>
@@ -25215,7 +25220,7 @@
         <v>364</v>
       </c>
       <c r="O176" s="26" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="P176" s="14"/>
       <c r="Q176" s="16" t="s">
@@ -25223,7 +25228,7 @@
       </c>
       <c r="R176" s="14"/>
     </row>
-    <row r="177" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:18" ht="175.5">
       <c r="A177" s="77">
         <f t="shared" ref="A177:B177" si="119">A176</f>
         <v>4</v>
@@ -25266,7 +25271,7 @@
         <v>373</v>
       </c>
       <c r="O177" s="26" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="P177" s="14"/>
       <c r="Q177" s="16" t="s">
@@ -25274,7 +25279,7 @@
       </c>
       <c r="R177" s="14"/>
     </row>
-    <row r="178" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:18" ht="136.5">
       <c r="A178" s="77">
         <f t="shared" ref="A178:G182" si="120">A177</f>
         <v>4</v>
@@ -25323,15 +25328,15 @@
         <v>377</v>
       </c>
       <c r="O178" s="26" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="P178" s="14"/>
       <c r="Q178" s="16" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="R178" s="14"/>
     </row>
-    <row r="179" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:18" ht="136.5">
       <c r="A179" s="77">
         <f t="shared" si="120"/>
         <v>4</v>
@@ -25380,7 +25385,7 @@
         <v>380</v>
       </c>
       <c r="O179" s="26" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="P179" s="14"/>
       <c r="Q179" s="16" t="s">
@@ -25388,7 +25393,7 @@
       </c>
       <c r="R179" s="14"/>
     </row>
-    <row r="180" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:18" ht="117">
       <c r="A180" s="77">
         <f t="shared" si="120"/>
         <v>4</v>
@@ -25436,7 +25441,7 @@
         <v>824</v>
       </c>
       <c r="O180" s="26" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="P180" s="14"/>
       <c r="Q180" s="16" t="s">
@@ -25444,7 +25449,7 @@
       </c>
       <c r="R180" s="14"/>
     </row>
-    <row r="181" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:18" ht="136.5">
       <c r="A181" s="77">
         <f t="shared" si="120"/>
         <v>4</v>
@@ -25493,7 +25498,7 @@
         <v>828</v>
       </c>
       <c r="O181" s="26" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="P181" s="14"/>
       <c r="Q181" s="16" t="s">
@@ -25501,7 +25506,7 @@
       </c>
       <c r="R181" s="14"/>
     </row>
-    <row r="182" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:18" ht="136.5">
       <c r="A182" s="77">
         <f t="shared" si="120"/>
         <v>4</v>
@@ -25550,7 +25555,7 @@
         <v>832</v>
       </c>
       <c r="O182" s="26" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="P182" s="14"/>
       <c r="Q182" s="16" t="s">
@@ -25558,7 +25563,7 @@
       </c>
       <c r="R182" s="14"/>
     </row>
-    <row r="183" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:18" ht="117">
       <c r="A183" s="77">
         <f t="shared" ref="A183:D183" si="123">A182</f>
         <v>4</v>
@@ -25591,7 +25596,7 @@
         <v>837</v>
       </c>
       <c r="J183" s="26" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="K183" s="26" t="str">
         <f t="shared" si="103"/>
@@ -25603,7 +25608,7 @@
         <v>838</v>
       </c>
       <c r="O183" s="26" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="P183" s="14"/>
       <c r="Q183" s="27" t="s">
@@ -25611,7 +25616,7 @@
       </c>
       <c r="R183" s="14"/>
     </row>
-    <row r="184" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:18" ht="117">
       <c r="A184" s="77">
         <f t="shared" ref="A184:G185" si="124">A183</f>
         <v>4</v>
@@ -25663,13 +25668,13 @@
         <v>840</v>
       </c>
       <c r="O184" s="26" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="P184" s="14"/>
       <c r="Q184" s="28"/>
       <c r="R184" s="15"/>
     </row>
-    <row r="185" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:18" ht="136.5">
       <c r="A185" s="77">
         <f t="shared" si="124"/>
         <v>4</v>
@@ -25718,18 +25723,18 @@
       <c r="L185" s="87"/>
       <c r="M185" s="87"/>
       <c r="N185" s="26" t="s">
-        <v>841</v>
+        <v>1204</v>
       </c>
       <c r="O185" s="26" t="s">
-        <v>1121</v>
+        <v>1205</v>
       </c>
       <c r="P185" s="14"/>
       <c r="Q185" s="27" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="R185" s="14"/>
     </row>
-    <row r="186" spans="1:18" ht="351" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:18" ht="351">
       <c r="A186" s="77">
         <f t="shared" ref="A186:D186" si="128">A185</f>
         <v>4</v>
@@ -25747,22 +25752,22 @@
         <v>プラットフォームセキュリティ</v>
       </c>
       <c r="E186" s="42" t="s">
+        <v>842</v>
+      </c>
+      <c r="F186" s="26" t="s">
         <v>843</v>
       </c>
-      <c r="F186" s="26" t="s">
+      <c r="G186" s="26" t="s">
         <v>844</v>
-      </c>
-      <c r="G186" s="26" t="s">
-        <v>845</v>
       </c>
       <c r="H186" s="26" t="s">
         <v>519</v>
       </c>
       <c r="I186" s="26" t="s">
+        <v>845</v>
+      </c>
+      <c r="J186" s="26" t="s">
         <v>846</v>
-      </c>
-      <c r="J186" s="26" t="s">
-        <v>847</v>
       </c>
       <c r="K186" s="26" t="str">
         <f t="shared" si="103"/>
@@ -25771,18 +25776,18 @@
       <c r="L186" s="87"/>
       <c r="M186" s="87"/>
       <c r="N186" s="26" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O186" s="26" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="P186" s="14"/>
       <c r="Q186" s="16" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R186" s="14"/>
     </row>
-    <row r="187" spans="1:18" ht="273" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:18" ht="273">
       <c r="A187" s="77">
         <f t="shared" ref="A187:G191" si="129">A186</f>
         <v>4</v>
@@ -25839,16 +25844,16 @@
       <c r="L187" s="87"/>
       <c r="M187" s="87"/>
       <c r="N187" s="26" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="O187" s="26" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="P187" s="14"/>
       <c r="Q187" s="28"/>
       <c r="R187" s="15"/>
     </row>
-    <row r="188" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:18" ht="117">
       <c r="A188" s="77">
         <f t="shared" si="129"/>
         <v>4</v>
@@ -25882,10 +25887,10 @@
         <v>★4</v>
       </c>
       <c r="I188" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="J188" s="26" t="s">
         <v>850</v>
-      </c>
-      <c r="J188" s="26" t="s">
-        <v>851</v>
       </c>
       <c r="K188" s="26" t="str">
         <f t="shared" si="103"/>
@@ -25894,16 +25899,16 @@
       <c r="L188" s="87"/>
       <c r="M188" s="87"/>
       <c r="N188" s="26" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O188" s="26" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="P188" s="14"/>
       <c r="Q188" s="28"/>
       <c r="R188" s="15"/>
     </row>
-    <row r="189" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:18" ht="175.5">
       <c r="A189" s="77">
         <f t="shared" si="129"/>
         <v>4</v>
@@ -25951,18 +25956,18 @@
       <c r="L189" s="87"/>
       <c r="M189" s="87"/>
       <c r="N189" s="26" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O189" s="26" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="P189" s="14"/>
       <c r="Q189" s="16" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="R189" s="14"/>
     </row>
-    <row r="190" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:18" ht="117">
       <c r="A190" s="77">
         <f t="shared" si="129"/>
         <v>4</v>
@@ -25996,10 +26001,10 @@
         <v>★4</v>
       </c>
       <c r="I190" s="26" t="s">
+        <v>854</v>
+      </c>
+      <c r="J190" s="26" t="s">
         <v>855</v>
-      </c>
-      <c r="J190" s="26" t="s">
-        <v>856</v>
       </c>
       <c r="K190" s="26" t="str">
         <f t="shared" si="103"/>
@@ -26008,18 +26013,18 @@
       <c r="L190" s="87"/>
       <c r="M190" s="87"/>
       <c r="N190" s="26" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O190" s="26" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="P190" s="14"/>
       <c r="Q190" s="27" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="R190" s="14"/>
     </row>
-    <row r="191" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:18" ht="117">
       <c r="A191" s="77">
         <f t="shared" si="129"/>
         <v>4</v>
@@ -26067,16 +26072,16 @@
       <c r="L191" s="87"/>
       <c r="M191" s="87"/>
       <c r="N191" s="26" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O191" s="26" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="P191" s="14"/>
       <c r="Q191" s="28"/>
       <c r="R191" s="15"/>
     </row>
-    <row r="192" spans="1:18" ht="292.5" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:18" ht="292.5">
       <c r="A192" s="77">
         <f t="shared" ref="A192:D192" si="131">A191</f>
         <v>4</v>
@@ -26109,7 +26114,7 @@
         <v>385</v>
       </c>
       <c r="J192" s="26" t="s">
-        <v>921</v>
+        <v>1202</v>
       </c>
       <c r="K192" s="26" t="str">
         <f t="shared" si="103"/>
@@ -26121,7 +26126,7 @@
         <v>386</v>
       </c>
       <c r="O192" s="26" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="P192" s="14"/>
       <c r="Q192" s="27" t="s">
@@ -26129,7 +26134,7 @@
       </c>
       <c r="R192" s="14"/>
     </row>
-    <row r="193" spans="1:18" ht="351" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:18" ht="351">
       <c r="A193" s="77">
         <f t="shared" ref="A193:G197" si="132">A192</f>
         <v>4</v>
@@ -26178,7 +26183,7 @@
         <v>390</v>
       </c>
       <c r="O193" s="26" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="P193" s="14"/>
       <c r="Q193" s="27" t="s">
@@ -26186,7 +26191,7 @@
       </c>
       <c r="R193" s="14"/>
     </row>
-    <row r="194" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:18" ht="117">
       <c r="A194" s="77">
         <f t="shared" si="132"/>
         <v>4</v>
@@ -26246,7 +26251,7 @@
         <v>392</v>
       </c>
       <c r="O194" s="26" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="P194" s="14"/>
       <c r="Q194" s="27" t="s">
@@ -26254,7 +26259,7 @@
       </c>
       <c r="R194" s="14"/>
     </row>
-    <row r="195" spans="1:18" ht="171" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:18" ht="171">
       <c r="A195" s="77">
         <f t="shared" si="132"/>
         <v>4</v>
@@ -26314,7 +26319,7 @@
         <v>394</v>
       </c>
       <c r="O195" s="26" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="P195" s="14"/>
       <c r="Q195" s="27" t="s">
@@ -26322,7 +26327,7 @@
       </c>
       <c r="R195" s="14"/>
     </row>
-    <row r="196" spans="1:18" ht="409.5" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:18" ht="409.5">
       <c r="A196" s="77">
         <f t="shared" si="132"/>
         <v>4</v>
@@ -26379,18 +26384,18 @@
       <c r="L196" s="87"/>
       <c r="M196" s="87"/>
       <c r="N196" s="26" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="O196" s="26" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="P196" s="14"/>
       <c r="Q196" s="27" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="R196" s="14"/>
     </row>
-    <row r="197" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:18" ht="156">
       <c r="A197" s="77">
         <f t="shared" si="132"/>
         <v>4</v>
@@ -26423,10 +26428,10 @@
         <v>519</v>
       </c>
       <c r="I197" s="26" t="s">
+        <v>859</v>
+      </c>
+      <c r="J197" s="26" t="s">
         <v>860</v>
-      </c>
-      <c r="J197" s="26" t="s">
-        <v>861</v>
       </c>
       <c r="K197" s="26" t="str">
         <f t="shared" si="136"/>
@@ -26435,16 +26440,16 @@
       <c r="L197" s="14"/>
       <c r="M197" s="14"/>
       <c r="N197" s="26" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O197" s="26" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="P197" s="14"/>
       <c r="Q197" s="28"/>
       <c r="R197" s="15"/>
     </row>
-    <row r="198" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:18" ht="136.5">
       <c r="A198" s="77">
         <f t="shared" ref="A198:D198" si="137">A197</f>
         <v>4</v>
@@ -26489,7 +26494,7 @@
         <v>401</v>
       </c>
       <c r="O198" s="26" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="P198" s="14"/>
       <c r="Q198" s="16" t="s">
@@ -26497,7 +26502,7 @@
       </c>
       <c r="R198" s="14"/>
     </row>
-    <row r="199" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:18" ht="117">
       <c r="A199" s="77">
         <f t="shared" ref="A199:G203" si="138">A198</f>
         <v>4</v>
@@ -26546,7 +26551,7 @@
         <v>405</v>
       </c>
       <c r="O199" s="26" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="P199" s="14"/>
       <c r="Q199" s="16" t="s">
@@ -26554,7 +26559,7 @@
       </c>
       <c r="R199" s="14"/>
     </row>
-    <row r="200" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:18" ht="175.5">
       <c r="A200" s="77">
         <f t="shared" si="138"/>
         <v>4</v>
@@ -26602,16 +26607,16 @@
       <c r="L200" s="87"/>
       <c r="M200" s="87"/>
       <c r="N200" s="26" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="O200" s="26" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="P200" s="14"/>
       <c r="Q200" s="28"/>
       <c r="R200" s="15"/>
     </row>
-    <row r="201" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:18" ht="136.5">
       <c r="A201" s="77">
         <f t="shared" si="138"/>
         <v>4</v>
@@ -26660,7 +26665,7 @@
         <v>409</v>
       </c>
       <c r="O201" s="26" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="P201" s="14"/>
       <c r="Q201" s="16" t="s">
@@ -26668,7 +26673,7 @@
       </c>
       <c r="R201" s="14"/>
     </row>
-    <row r="202" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:18" ht="136.5">
       <c r="A202" s="77">
         <f t="shared" si="138"/>
         <v>4</v>
@@ -26701,10 +26706,10 @@
         <v>519</v>
       </c>
       <c r="I202" s="26" t="s">
+        <v>862</v>
+      </c>
+      <c r="J202" s="26" t="s">
         <v>863</v>
-      </c>
-      <c r="J202" s="26" t="s">
-        <v>864</v>
       </c>
       <c r="K202" s="26" t="str">
         <f t="shared" si="136"/>
@@ -26713,18 +26718,18 @@
       <c r="L202" s="14"/>
       <c r="M202" s="14"/>
       <c r="N202" s="26" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="O202" s="26" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="P202" s="14"/>
       <c r="Q202" s="16" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="R202" s="14"/>
     </row>
-    <row r="203" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:18" ht="156">
       <c r="A203" s="77">
         <f t="shared" si="138"/>
         <v>4</v>
@@ -26758,10 +26763,10 @@
         <v>★4</v>
       </c>
       <c r="I203" s="26" t="s">
+        <v>866</v>
+      </c>
+      <c r="J203" s="26" t="s">
         <v>867</v>
-      </c>
-      <c r="J203" s="26" t="s">
-        <v>868</v>
       </c>
       <c r="K203" s="26" t="str">
         <f t="shared" si="136"/>
@@ -26770,18 +26775,18 @@
       <c r="L203" s="14"/>
       <c r="M203" s="14"/>
       <c r="N203" s="26" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O203" s="26" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="P203" s="14"/>
       <c r="Q203" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="R203" s="14"/>
     </row>
-    <row r="204" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:18" ht="175.5">
       <c r="A204" s="77">
         <f t="shared" ref="A204:B204" si="140">A203</f>
         <v>4</v>
@@ -26824,7 +26829,7 @@
         <v>418</v>
       </c>
       <c r="O204" s="26" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="P204" s="14"/>
       <c r="Q204" s="16" t="s">
@@ -26832,7 +26837,7 @@
       </c>
       <c r="R204" s="14"/>
     </row>
-    <row r="205" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:18" ht="136.5">
       <c r="A205" s="77">
         <f t="shared" ref="A205:A213" si="141">A204</f>
         <v>4</v>
@@ -26881,7 +26886,7 @@
         <v>422</v>
       </c>
       <c r="O205" s="26" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="P205" s="14"/>
       <c r="Q205" s="27" t="s">
@@ -26889,7 +26894,7 @@
       </c>
       <c r="R205" s="14"/>
     </row>
-    <row r="206" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:18" ht="156">
       <c r="A206" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -26938,7 +26943,7 @@
         <v>426</v>
       </c>
       <c r="O206" s="26" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="P206" s="14"/>
       <c r="Q206" s="16" t="s">
@@ -26946,7 +26951,7 @@
       </c>
       <c r="R206" s="14"/>
     </row>
-    <row r="207" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:18" ht="156">
       <c r="A207" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -26995,7 +27000,7 @@
         <v>430</v>
       </c>
       <c r="O207" s="26" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="P207" s="14"/>
       <c r="Q207" s="16" t="s">
@@ -27003,7 +27008,7 @@
       </c>
       <c r="R207" s="14"/>
     </row>
-    <row r="208" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:18" ht="175.5">
       <c r="A208" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27052,7 +27057,7 @@
         <v>434</v>
       </c>
       <c r="O208" s="26" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="P208" s="14"/>
       <c r="Q208" s="27" t="s">
@@ -27060,7 +27065,7 @@
       </c>
       <c r="R208" s="14"/>
     </row>
-    <row r="209" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:18" ht="156">
       <c r="A209" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27109,7 +27114,7 @@
         <v>438</v>
       </c>
       <c r="O209" s="26" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="P209" s="14"/>
       <c r="Q209" s="16" t="s">
@@ -27117,7 +27122,7 @@
       </c>
       <c r="R209" s="14"/>
     </row>
-    <row r="210" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:18" ht="175.5">
       <c r="A210" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27166,7 +27171,7 @@
         <v>442</v>
       </c>
       <c r="O210" s="26" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="P210" s="14"/>
       <c r="Q210" s="16" t="s">
@@ -27174,7 +27179,7 @@
       </c>
       <c r="R210" s="14"/>
     </row>
-    <row r="211" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:18" ht="136.5">
       <c r="A211" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27207,10 +27212,10 @@
         <v>519</v>
       </c>
       <c r="I211" s="26" t="s">
+        <v>870</v>
+      </c>
+      <c r="J211" s="26" t="s">
         <v>871</v>
-      </c>
-      <c r="J211" s="26" t="s">
-        <v>872</v>
       </c>
       <c r="K211" s="26" t="str">
         <f t="shared" si="136"/>
@@ -27219,18 +27224,18 @@
       <c r="L211" s="14"/>
       <c r="M211" s="14"/>
       <c r="N211" s="26" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="O211" s="26" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="P211" s="14"/>
       <c r="Q211" s="16" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R211" s="14"/>
     </row>
-    <row r="212" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:18" ht="117">
       <c r="A212" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27264,10 +27269,10 @@
         <v>★4</v>
       </c>
       <c r="I212" s="26" t="s">
+        <v>874</v>
+      </c>
+      <c r="J212" s="26" t="s">
         <v>875</v>
-      </c>
-      <c r="J212" s="26" t="s">
-        <v>876</v>
       </c>
       <c r="K212" s="26" t="str">
         <f t="shared" si="136"/>
@@ -27276,18 +27281,18 @@
       <c r="L212" s="87"/>
       <c r="M212" s="87"/>
       <c r="N212" s="26" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O212" s="26" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="P212" s="14"/>
       <c r="Q212" s="16" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R212" s="14"/>
     </row>
-    <row r="213" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:18" ht="117">
       <c r="A213" s="77">
         <f t="shared" si="141"/>
         <v>4</v>
@@ -27335,18 +27340,18 @@
       <c r="L213" s="87"/>
       <c r="M213" s="87"/>
       <c r="N213" s="26" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O213" s="26" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="P213" s="14"/>
       <c r="Q213" s="16" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R213" s="14"/>
     </row>
-    <row r="214" spans="1:18" ht="175.5" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:18" ht="175.5">
       <c r="A214" s="44">
         <v>5</v>
       </c>
@@ -27386,7 +27391,7 @@
         <v>453</v>
       </c>
       <c r="O214" s="26" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="P214" s="14"/>
       <c r="Q214" s="16" t="s">
@@ -27394,7 +27399,7 @@
       </c>
       <c r="R214" s="14"/>
     </row>
-    <row r="215" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:18" ht="117">
       <c r="A215" s="76">
         <f t="shared" ref="A215:G218" si="151">A214</f>
         <v>5</v>
@@ -27443,13 +27448,13 @@
         <v>457</v>
       </c>
       <c r="O215" s="26" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="P215" s="14"/>
       <c r="Q215" s="28"/>
       <c r="R215" s="15"/>
     </row>
-    <row r="216" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:18" ht="195">
       <c r="A216" s="76">
         <f t="shared" si="151"/>
         <v>5</v>
@@ -27500,7 +27505,7 @@
         <v>458</v>
       </c>
       <c r="O216" s="26" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="P216" s="14"/>
       <c r="Q216" s="16" t="s">
@@ -27508,7 +27513,7 @@
       </c>
       <c r="R216" s="14"/>
     </row>
-    <row r="217" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:18" ht="156">
       <c r="A217" s="76">
         <f t="shared" si="151"/>
         <v>5</v>
@@ -27559,7 +27564,7 @@
         <v>460</v>
       </c>
       <c r="O217" s="26" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="P217" s="14"/>
       <c r="Q217" s="16" t="s">
@@ -27567,7 +27572,7 @@
       </c>
       <c r="R217" s="14"/>
     </row>
-    <row r="218" spans="1:18" ht="195" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:18" ht="195">
       <c r="A218" s="76">
         <f t="shared" si="151"/>
         <v>5</v>
@@ -27616,7 +27621,7 @@
         <v>464</v>
       </c>
       <c r="O218" s="26" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="P218" s="14"/>
       <c r="Q218" s="16" t="s">
@@ -27624,7 +27629,7 @@
       </c>
       <c r="R218" s="14"/>
     </row>
-    <row r="219" spans="1:18" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:18" ht="214.5">
       <c r="A219" s="76">
         <f t="shared" ref="A219:D219" si="156">A218</f>
         <v>5</v>
@@ -27642,22 +27647,22 @@
         <v>継続的監視</v>
       </c>
       <c r="E219" s="44" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F219" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="H219" s="26" t="s">
         <v>519</v>
       </c>
       <c r="I219" s="26" t="s">
+        <v>881</v>
+      </c>
+      <c r="J219" s="26" t="s">
         <v>882</v>
-      </c>
-      <c r="J219" s="26" t="s">
-        <v>883</v>
       </c>
       <c r="K219" s="26" t="str">
         <f t="shared" si="153"/>
@@ -27666,18 +27671,18 @@
       <c r="L219" s="14"/>
       <c r="M219" s="14"/>
       <c r="N219" s="26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="O219" s="26" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="P219" s="14"/>
       <c r="Q219" s="16" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="R219" s="14"/>
     </row>
-    <row r="220" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:18" ht="136.5">
       <c r="A220" s="76">
         <f t="shared" ref="A220:G221" si="157">A219</f>
         <v>5</v>
@@ -27711,10 +27716,10 @@
         <v>★4</v>
       </c>
       <c r="I220" s="26" t="s">
+        <v>885</v>
+      </c>
+      <c r="J220" s="26" t="s">
         <v>886</v>
-      </c>
-      <c r="J220" s="26" t="s">
-        <v>887</v>
       </c>
       <c r="K220" s="26" t="str">
         <f t="shared" si="153"/>
@@ -27723,18 +27728,18 @@
       <c r="L220" s="14"/>
       <c r="M220" s="14"/>
       <c r="N220" s="26" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="O220" s="26" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="P220" s="14"/>
       <c r="Q220" s="27" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R220" s="14"/>
     </row>
-    <row r="221" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:18" ht="156">
       <c r="A221" s="76">
         <f t="shared" si="157"/>
         <v>5</v>
@@ -27768,10 +27773,10 @@
         <v>★4</v>
       </c>
       <c r="I221" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="J221" s="26" t="s">
         <v>890</v>
-      </c>
-      <c r="J221" s="26" t="s">
-        <v>891</v>
       </c>
       <c r="K221" s="26" t="str">
         <f t="shared" si="153"/>
@@ -27780,18 +27785,18 @@
       <c r="L221" s="14"/>
       <c r="M221" s="14"/>
       <c r="N221" s="26" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="O221" s="26" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="P221" s="14"/>
       <c r="Q221" s="16" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="R221" s="14"/>
     </row>
-    <row r="222" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:18" ht="117">
       <c r="A222" s="76">
         <f t="shared" ref="A222:B222" si="159">A221</f>
         <v>5</v>
@@ -27801,28 +27806,28 @@
         <v>攻撃等の検知</v>
       </c>
       <c r="C222" s="44" t="s">
+        <v>893</v>
+      </c>
+      <c r="D222" s="44" t="s">
         <v>894</v>
       </c>
-      <c r="D222" s="44" t="s">
+      <c r="E222" s="44" t="s">
         <v>895</v>
       </c>
-      <c r="E222" s="44" t="s">
+      <c r="F222" s="26" t="s">
         <v>896</v>
       </c>
-      <c r="F222" s="26" t="s">
+      <c r="G222" s="26" t="s">
         <v>897</v>
-      </c>
-      <c r="G222" s="26" t="s">
-        <v>898</v>
       </c>
       <c r="H222" s="26" t="s">
         <v>519</v>
       </c>
       <c r="I222" s="26" t="s">
+        <v>898</v>
+      </c>
+      <c r="J222" s="26" t="s">
         <v>899</v>
-      </c>
-      <c r="J222" s="26" t="s">
-        <v>900</v>
       </c>
       <c r="K222" s="26" t="str">
         <f t="shared" si="153"/>
@@ -27831,16 +27836,16 @@
       <c r="L222" s="87"/>
       <c r="M222" s="87"/>
       <c r="N222" s="26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="O222" s="26" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="P222" s="14"/>
       <c r="Q222" s="28"/>
       <c r="R222" s="15"/>
     </row>
-    <row r="223" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:18" ht="156">
       <c r="A223" s="76">
         <f t="shared" ref="A223:G224" si="160">A222</f>
         <v>5</v>
@@ -27888,18 +27893,18 @@
       <c r="L223" s="87"/>
       <c r="M223" s="87"/>
       <c r="N223" s="26" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="O223" s="26" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="P223" s="14"/>
       <c r="Q223" s="16" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="R223" s="14"/>
     </row>
-    <row r="224" spans="1:18" ht="214.5" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:18" ht="214.5">
       <c r="A224" s="76">
         <f t="shared" si="160"/>
         <v>5</v>
@@ -27933,10 +27938,10 @@
         <v>★4</v>
       </c>
       <c r="I224" s="26" t="s">
+        <v>903</v>
+      </c>
+      <c r="J224" s="26" t="s">
         <v>904</v>
-      </c>
-      <c r="J224" s="26" t="s">
-        <v>905</v>
       </c>
       <c r="K224" s="26" t="str">
         <f t="shared" si="153"/>
@@ -27945,18 +27950,18 @@
       <c r="L224" s="14"/>
       <c r="M224" s="14"/>
       <c r="N224" s="26" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="O224" s="26" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="P224" s="14"/>
       <c r="Q224" s="16" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="R224" s="14"/>
     </row>
-    <row r="225" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:18" ht="117">
       <c r="A225" s="45">
         <v>6</v>
       </c>
@@ -27996,7 +28001,7 @@
         <v>475</v>
       </c>
       <c r="O225" s="26" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="P225" s="14"/>
       <c r="Q225" s="16" t="s">
@@ -28004,7 +28009,7 @@
       </c>
       <c r="R225" s="14"/>
     </row>
-    <row r="226" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:18" ht="117">
       <c r="A226" s="75">
         <f t="shared" ref="A226:G233" si="162">A225</f>
         <v>6</v>
@@ -28057,13 +28062,13 @@
         <v>477</v>
       </c>
       <c r="O226" s="26" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="P226" s="14"/>
       <c r="Q226" s="28"/>
       <c r="R226" s="15"/>
     </row>
-    <row r="227" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:18" ht="156">
       <c r="A227" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28112,7 +28117,7 @@
         <v>480</v>
       </c>
       <c r="O227" s="26" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="P227" s="14"/>
       <c r="Q227" s="16" t="s">
@@ -28120,7 +28125,7 @@
       </c>
       <c r="R227" s="14"/>
     </row>
-    <row r="228" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:18" ht="117">
       <c r="A228" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28171,13 +28176,13 @@
         <v>482</v>
       </c>
       <c r="O228" s="26" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="P228" s="14"/>
       <c r="Q228" s="28"/>
       <c r="R228" s="15"/>
     </row>
-    <row r="229" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:18" ht="156">
       <c r="A229" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28226,7 +28231,7 @@
         <v>485</v>
       </c>
       <c r="O229" s="26" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="P229" s="14"/>
       <c r="Q229" s="16" t="s">
@@ -28234,7 +28239,7 @@
       </c>
       <c r="R229" s="14"/>
     </row>
-    <row r="230" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:18" ht="136.5">
       <c r="A230" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28283,7 +28288,7 @@
         <v>489</v>
       </c>
       <c r="O230" s="26" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="P230" s="14"/>
       <c r="Q230" s="27" t="s">
@@ -28291,7 +28296,7 @@
       </c>
       <c r="R230" s="14"/>
     </row>
-    <row r="231" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:18" ht="136.5">
       <c r="A231" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28340,7 +28345,7 @@
         <v>493</v>
       </c>
       <c r="O231" s="26" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="P231" s="14"/>
       <c r="Q231" s="16" t="s">
@@ -28348,7 +28353,7 @@
       </c>
       <c r="R231" s="14"/>
     </row>
-    <row r="232" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:18" ht="156">
       <c r="A232" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28397,7 +28402,7 @@
         <v>497</v>
       </c>
       <c r="O232" s="26" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="P232" s="14"/>
       <c r="Q232" s="16" t="s">
@@ -28405,7 +28410,7 @@
       </c>
       <c r="R232" s="14"/>
     </row>
-    <row r="233" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:18" ht="156">
       <c r="A233" s="75">
         <f t="shared" si="162"/>
         <v>6</v>
@@ -28456,7 +28461,7 @@
         <v>499</v>
       </c>
       <c r="O233" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="P233" s="14"/>
       <c r="Q233" s="16" t="s">
@@ -28464,7 +28469,7 @@
       </c>
       <c r="R233" s="14"/>
     </row>
-    <row r="234" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:18" ht="156">
       <c r="A234" s="46">
         <v>7</v>
       </c>
@@ -28504,7 +28509,7 @@
         <v>510</v>
       </c>
       <c r="O234" s="26" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="P234" s="14"/>
       <c r="Q234" s="27" t="s">
@@ -28512,7 +28517,7 @@
       </c>
       <c r="R234" s="14"/>
     </row>
-    <row r="235" spans="1:18" ht="117" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:18" ht="117">
       <c r="A235" s="74">
         <f t="shared" ref="A235:G237" si="166">A234</f>
         <v>7</v>
@@ -28566,7 +28571,7 @@
         <v>512</v>
       </c>
       <c r="O235" s="26" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="P235" s="14"/>
       <c r="Q235" s="27" t="s">
@@ -28574,7 +28579,7 @@
       </c>
       <c r="R235" s="14"/>
     </row>
-    <row r="236" spans="1:18" ht="136.5" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:18" ht="136.5">
       <c r="A236" s="74">
         <f t="shared" si="166"/>
         <v>7</v>
@@ -28607,10 +28612,10 @@
         <v>519</v>
       </c>
       <c r="I236" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="J236" s="26" t="s">
         <v>908</v>
-      </c>
-      <c r="J236" s="26" t="s">
-        <v>909</v>
       </c>
       <c r="K236" s="26" t="str">
         <f t="shared" si="167"/>
@@ -28619,18 +28624,18 @@
       <c r="L236" s="87"/>
       <c r="M236" s="87"/>
       <c r="N236" s="26" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="O236" s="26" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="P236" s="14"/>
       <c r="Q236" s="16" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="R236" s="14"/>
     </row>
-    <row r="237" spans="1:18" ht="156" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:18" ht="156">
       <c r="A237" s="74">
         <f t="shared" si="166"/>
         <v>7</v>
@@ -28680,27 +28685,27 @@
       <c r="L237" s="87"/>
       <c r="M237" s="87"/>
       <c r="N237" s="26" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="O237" s="26" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="P237" s="14"/>
       <c r="Q237" s="28"/>
       <c r="R237" s="15"/>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:18">
       <c r="K238" s="13"/>
       <c r="M238" s="12"/>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:18">
       <c r="H239" s="13"/>
       <c r="I239" s="13"/>
       <c r="J239" s="13"/>
       <c r="K239" s="13"/>
       <c r="M239" s="12"/>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:18">
       <c r="H240" s="13"/>
       <c r="I240" s="13"/>
       <c r="J240" s="13"/>
@@ -28742,7 +28747,7 @@
       <formula>N15=N14</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L15:L237" xr:uid="{66EE34D4-B716-4734-A6FB-FE399BB4F407}">
       <formula1>"○"</formula1>
     </dataValidation>
